--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1408</v>
+        <v>20.3893</v>
       </c>
       <c r="E2" t="n">
-        <v>14.788</v>
+        <v>10.1257</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3526</v>
+        <v>10.2636</v>
       </c>
       <c r="G2" t="n">
-        <v>9.1782</v>
+        <v>19.1977</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9826</v>
+        <v>15.1109</v>
       </c>
       <c r="I2" t="n">
-        <v>5.195600000000001</v>
+        <v>4.087000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>9.9254</v>
+        <v>17.9593</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3368</v>
+        <v>13.8589</v>
       </c>
       <c r="L2" t="n">
-        <v>6.5884</v>
+        <v>4.1004</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7472000000000001</v>
+        <v>1.2384</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6456</v>
+        <v>1.252</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3928</v>
+        <v>-0.01349999999999996</v>
       </c>
       <c r="P2" t="n">
-        <v>6.4612</v>
+        <v>-5.1298</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-16.3217</v>
       </c>
       <c r="R2" t="n">
-        <v>6.4612</v>
+        <v>11.1921</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8678</v>
+        <v>-0.4791</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8144</v>
+        <v>1.5505</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0534</v>
+        <v>-2.0297</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3694</v>
+        <v>6.8005</v>
       </c>
       <c r="W2" t="n">
-        <v>5.6774</v>
+        <v>6.9378</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.308</v>
+        <v>-0.1373</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>15.0708</v>
+        <v>16.0092</v>
       </c>
       <c r="E3" t="n">
-        <v>3.490200000000001</v>
+        <v>14.4686</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5804</v>
+        <v>1.5404</v>
       </c>
       <c r="G3" t="n">
-        <v>14.2168</v>
+        <v>9.3231</v>
       </c>
       <c r="H3" t="n">
-        <v>9.695</v>
+        <v>4.1255</v>
       </c>
       <c r="I3" t="n">
-        <v>4.521599999999999</v>
+        <v>5.1976</v>
       </c>
       <c r="J3" t="n">
-        <v>11.3274</v>
+        <v>9.772600000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7034</v>
+        <v>3.2394</v>
       </c>
       <c r="L3" t="n">
-        <v>3.6242</v>
+        <v>6.5334</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8892</v>
+        <v>-0.4495</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9916</v>
+        <v>0.8861</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8974</v>
+        <v>-1.336</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.6922</v>
+        <v>6.5288</v>
       </c>
       <c r="Q3" t="n">
-        <v>-13.8452</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>10.1532</v>
+        <v>6.5288</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.839</v>
+        <v>-1.1845</v>
       </c>
       <c r="T3" t="n">
-        <v>0.623</v>
+        <v>-0.9154</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.462</v>
+        <v>-0.2691</v>
       </c>
       <c r="V3" t="n">
-        <v>5.385</v>
+        <v>1.3418</v>
       </c>
       <c r="W3" t="n">
-        <v>5.385</v>
+        <v>5.6112</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-4.2694</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>14.7914</v>
+        <v>14.2681</v>
       </c>
       <c r="E4" t="n">
-        <v>10.4954</v>
+        <v>15.2434</v>
       </c>
       <c r="F4" t="n">
-        <v>4.296</v>
+        <v>-0.9749000000000003</v>
       </c>
       <c r="G4" t="n">
-        <v>15.6168</v>
+        <v>5.5392</v>
       </c>
       <c r="H4" t="n">
-        <v>10.0772</v>
+        <v>8.5389</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5396</v>
+        <v>-2.9997</v>
       </c>
       <c r="J4" t="n">
-        <v>10.7794</v>
+        <v>10.5755</v>
       </c>
       <c r="K4" t="n">
-        <v>7.4086</v>
+        <v>8.805199999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3708</v>
+        <v>1.7703</v>
       </c>
       <c r="M4" t="n">
-        <v>4.837400000000001</v>
+        <v>-5.0365</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6686</v>
+        <v>-0.2663</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1688</v>
+        <v>-4.77</v>
       </c>
       <c r="P4" t="n">
-        <v>3.692</v>
+        <v>7.6944</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3076</v>
+        <v>-1.1658</v>
       </c>
       <c r="R4" t="n">
-        <v>5.9996</v>
+        <v>8.860300000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9442</v>
+        <v>0.8972</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6542</v>
+        <v>2.3569</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2902</v>
+        <v>-1.4597</v>
       </c>
       <c r="V4" t="n">
-        <v>-6.461799999999999</v>
+        <v>0.1372000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3694</v>
+        <v>3.4765</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.8312</v>
+        <v>-3.3392</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>10.5896</v>
+        <v>11.5642</v>
       </c>
       <c r="E5" t="n">
-        <v>9.641</v>
+        <v>4.368600000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9486000000000003</v>
+        <v>7.1954</v>
       </c>
       <c r="G5" t="n">
-        <v>3.127</v>
+        <v>7.0305</v>
       </c>
       <c r="H5" t="n">
-        <v>7.277600000000001</v>
+        <v>8.5024</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.1506</v>
+        <v>-1.4719</v>
       </c>
       <c r="J5" t="n">
-        <v>6.5572</v>
+        <v>9.490500000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>6.9686</v>
+        <v>7.587400000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4113999999999999</v>
+        <v>1.9033</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.4302</v>
+        <v>-2.46</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3089999999999999</v>
+        <v>0.9153</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.739199999999999</v>
+        <v>-3.3752</v>
       </c>
       <c r="P5" t="n">
-        <v>7.8456</v>
+        <v>2.3317</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-9.326700000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>7.8456</v>
+        <v>11.6584</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4014</v>
+        <v>1.4089</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7144</v>
+        <v>1.0026</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.313</v>
+        <v>0.4063</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7846</v>
+        <v>0.7927999999999997</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3694</v>
+        <v>3.2019</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.154</v>
+        <v>-2.4091</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>8.097799999999999</v>
+        <v>9.077500000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3019999999999999</v>
+        <v>4.0146</v>
       </c>
       <c r="F6" t="n">
-        <v>8.4</v>
+        <v>5.0632</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8088</v>
+        <v>9.970700000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>4.966</v>
+        <v>6.6033</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1572</v>
+        <v>3.3671</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3408</v>
+        <v>6.806699999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9742</v>
+        <v>3.5283</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3666</v>
+        <v>3.278</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5322</v>
+        <v>3.164000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>1.9916</v>
+        <v>3.075</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.524</v>
+        <v>0.08899999999999952</v>
       </c>
       <c r="P6" t="n">
-        <v>3.2306</v>
+        <v>1.6321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.9226</v>
+        <v>-5.8291</v>
       </c>
       <c r="R6" t="n">
-        <v>10.1532</v>
+        <v>7.4612</v>
       </c>
       <c r="S6" t="n">
-        <v>0.274</v>
+        <v>3.7416</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1256</v>
+        <v>1.5581</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1484</v>
+        <v>2.1835</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7846</v>
+        <v>-6.266500000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>2.154</v>
+        <v>1.4791</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3694</v>
+        <v>-7.7458</v>
       </c>
     </row>
     <row r="7">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6966</v>
+        <v>5.585500000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.158600000000001</v>
+        <v>-2.490600000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>8.8552</v>
+        <v>8.0761</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.633599999999999</v>
+        <v>-0.2059999999999997</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.383599999999999</v>
+        <v>-0.7071999999999994</v>
       </c>
       <c r="I7" t="n">
-        <v>1.75</v>
+        <v>0.5011000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-5.4672</v>
+        <v>-2.6936</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.058</v>
+        <v>-3.6106</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5906</v>
+        <v>0.9171</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8338</v>
+        <v>2.4875</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6746</v>
+        <v>2.9035</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1592</v>
+        <v>-0.4160999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>4.1534</v>
+        <v>4.197000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3076</v>
+        <v>-3.4974</v>
       </c>
       <c r="R7" t="n">
-        <v>6.461</v>
+        <v>7.6946</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2378</v>
+        <v>4.369</v>
       </c>
       <c r="T7" t="n">
-        <v>3.308</v>
+        <v>4.4623</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07040000000000013</v>
+        <v>-0.09309999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0612</v>
+        <v>-2.7747</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6918</v>
+        <v>-0.7618</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3694</v>
+        <v>-2.0129</v>
       </c>
     </row>
     <row r="8">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8779999999999999</v>
+        <v>0.5034000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.591</v>
+        <v>-1.9981</v>
       </c>
       <c r="F8" t="n">
-        <v>4.469200000000001</v>
+        <v>2.5017</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.6656</v>
+        <v>-10.8939</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.344</v>
+        <v>-2.6922</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.3216</v>
+        <v>-8.201700000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-10.126</v>
+        <v>-8.025400000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.6646</v>
+        <v>-2.928</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.4614</v>
+        <v>-5.0976</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5396000000000001</v>
+        <v>-2.8687</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3206</v>
+        <v>0.2357999999999998</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8602</v>
+        <v>-3.104299999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>8.3072</v>
+        <v>7.2282</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3317</v>
       </c>
       <c r="R8" t="n">
-        <v>8.3072</v>
+        <v>9.559799999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>1.375</v>
+        <v>2.3092</v>
       </c>
       <c r="T8" t="n">
-        <v>2.719</v>
+        <v>3.4034</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.344</v>
+        <v>-1.0942</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8616</v>
+        <v>1.86</v>
       </c>
       <c r="W8" t="n">
-        <v>3.8158</v>
+        <v>4.9556</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.9542</v>
+        <v>-3.0956</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2732</v>
+        <v>0.1438</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4816</v>
+        <v>2.6204</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7914</v>
+        <v>-2.4766</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8678</v>
+        <v>-0.8222</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3422</v>
+        <v>0.4278</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5256</v>
+        <v>-1.25</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.2078</v>
+        <v>2.1227</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6728</v>
+        <v>1.4181</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.535</v>
+        <v>0.7046</v>
       </c>
       <c r="M9" t="n">
-        <v>0.34</v>
+        <v>-2.9449</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3306</v>
+        <v>-0.9903</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0094</v>
+        <v>-1.9546</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1658</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.113</v>
+        <v>0.8675</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7262</v>
+        <v>0.4977</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.839</v>
+        <v>0.3698</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2924</v>
+        <v>-1.0673</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2924</v>
+        <v>-1.0673</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6674</v>
+        <v>-3.252</v>
       </c>
       <c r="E10" t="n">
-        <v>-13.724</v>
+        <v>-2.5504</v>
       </c>
       <c r="F10" t="n">
-        <v>10.0566</v>
+        <v>-0.7018</v>
       </c>
       <c r="G10" t="n">
-        <v>6.209200000000001</v>
+        <v>-2.8542</v>
       </c>
       <c r="H10" t="n">
-        <v>6.2906</v>
+        <v>-1.353</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08119999999999994</v>
+        <v>-1.5012</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8392</v>
+        <v>-3.2358</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6218</v>
+        <v>-1.699</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7828</v>
+        <v>-1.5368</v>
       </c>
       <c r="M10" t="n">
-        <v>4.37</v>
+        <v>0.3816</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6688</v>
+        <v>0.346</v>
       </c>
       <c r="O10" t="n">
-        <v>1.7014</v>
+        <v>0.0356</v>
       </c>
       <c r="P10" t="n">
-        <v>-11.0762</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-16.1528</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5.0766</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9544000000000001</v>
+        <v>-0.1232</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5644</v>
+        <v>0.6854</v>
       </c>
       <c r="U10" t="n">
-        <v>0.61</v>
+        <v>-0.8088</v>
       </c>
       <c r="V10" t="n">
-        <v>2.154</v>
+        <v>-0.2746</v>
       </c>
       <c r="W10" t="n">
-        <v>2.154</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2746</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. CARDENAS</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2146</v>
+        <v>-3.8007</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.801</v>
+        <v>-13.4449</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4136</v>
+        <v>9.6442</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9128</v>
+        <v>4.484</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.88</v>
+        <v>6.5721</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.033</v>
+        <v>-2.0881</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.08279999999999998</v>
+        <v>2.0073</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.517799999999999</v>
+        <v>3.1622</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4348</v>
+        <v>-1.1549</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8298</v>
+        <v>2.4767</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.362</v>
+        <v>3.41</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4678</v>
+        <v>-0.9335</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3846</v>
+        <v>-10.0262</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.6152</v>
+        <v>-16.3218</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2306</v>
+        <v>6.2956</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.625</v>
+        <v>-0.5306</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.103</v>
+        <v>-1.4024</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5218</v>
+        <v>0.872</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2924</v>
+        <v>2.2719</v>
       </c>
       <c r="W11" t="n">
+        <v>2.2719</v>
+      </c>
+      <c r="X11" t="n">
         <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.2924</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>A. CARDENAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,148 +1342,226 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.9138</v>
+        <v>-7.9418</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.6992</v>
+        <v>-5.5171</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7852</v>
+        <v>-2.4247</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8834</v>
+        <v>-5.1733</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.548</v>
+        <v>-2.7682</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6646000000000001</v>
+        <v>-2.4051</v>
       </c>
       <c r="J12" t="n">
-        <v>-7.776600000000001</v>
+        <v>-0.5487000000000002</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.8802</v>
+        <v>-2.9793</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8964000000000003</v>
+        <v>2.4306</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8932</v>
+        <v>-4.6246</v>
       </c>
       <c r="N12" t="n">
-        <v>2.332</v>
+        <v>0.2111</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5612</v>
+        <v>-4.836</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3844</v>
+        <v>-1.399</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.615</v>
+        <v>-5.829</v>
       </c>
       <c r="R12" t="n">
-        <v>3.2306</v>
+        <v>4.43</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1996</v>
+        <v>-1.0949</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6926000000000001</v>
+        <v>-0.2065</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8922</v>
+        <v>-0.8883</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4464</v>
+        <v>-0.2746</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0673</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4464</v>
+        <v>-1.3419</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>S. DE LARREA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Valencia Basket</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-12.2616</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-13.9781</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.7165</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-8.711500000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-4.8003</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-3.9108</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-11.3522</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-7.7069</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-3.6453</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.6411</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.9065</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.2654999999999998</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.2332000000000001</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-4.6634</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-1.0449</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.8331</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1.8782</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-2.2719</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.2046</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-3.4765</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Valencia Basket</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>47.196</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-3.342799999999993</v>
-      </c>
-      <c r="F13" t="n">
-        <v>50.53880000000001</v>
-      </c>
-      <c r="G13" t="n">
-        <v>30.1936</v>
-      </c>
-      <c r="H13" t="n">
-        <v>28.7912</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.402200000000001</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18.10899999999999</v>
-      </c>
-      <c r="K13" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5.888400000000001</v>
-      </c>
-      <c r="M13" t="n">
-        <v>12.0846</v>
-      </c>
-      <c r="N13" t="n">
-        <v>16.571</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-4.486599999999999</v>
-      </c>
-      <c r="P13" t="n">
-        <v>16.1526</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-50.766</v>
-      </c>
-      <c r="R13" t="n">
-        <v>66.9188</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.6336</v>
-      </c>
-      <c r="T13" t="n">
-        <v>8.081200000000001</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-6.4472</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-0.7842000000000002</v>
-      </c>
-      <c r="W13" t="n">
-        <v>21.2332</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-22.0174</v>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50.28489999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10.8621</v>
+      </c>
+      <c r="F14" t="n">
+        <v>39.42310000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>26.88410000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-10.6757</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32.8789</v>
+      </c>
+      <c r="K14" t="n">
+        <v>22.6757</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10.2031</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-5.994899999999999</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14.8847</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-20.8801</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13.9898</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-65.28660000000001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>79.27660000000003</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9.136200000000001</v>
+      </c>
+      <c r="T14" t="n">
+        <v>13.8257</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-4.689500000000001</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.2745999999999991</v>
+      </c>
+      <c r="W14" t="n">
+        <v>29.4441</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-29.1696</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.3893</v>
+        <v>13.1625</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1257</v>
+        <v>9.4185</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2636</v>
+        <v>3.7442</v>
       </c>
       <c r="G2" t="n">
-        <v>19.1977</v>
+        <v>12.2231</v>
       </c>
       <c r="H2" t="n">
-        <v>15.1109</v>
+        <v>10.3269</v>
       </c>
       <c r="I2" t="n">
-        <v>4.087000000000001</v>
+        <v>1.8963</v>
       </c>
       <c r="J2" t="n">
-        <v>17.9593</v>
+        <v>13.2361</v>
       </c>
       <c r="K2" t="n">
-        <v>13.8589</v>
+        <v>10.4648</v>
       </c>
       <c r="L2" t="n">
-        <v>4.1004</v>
+        <v>2.7713</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2384</v>
+        <v>-1.0131</v>
       </c>
       <c r="N2" t="n">
-        <v>1.252</v>
+        <v>-0.1379</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.01349999999999996</v>
+        <v>-0.8751000000000002</v>
       </c>
       <c r="P2" t="n">
-        <v>-5.1298</v>
+        <v>-3.213</v>
       </c>
       <c r="Q2" t="n">
-        <v>-16.3217</v>
+        <v>-9.1798</v>
       </c>
       <c r="R2" t="n">
-        <v>11.1921</v>
+        <v>5.9669</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4791</v>
+        <v>-0.0247</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5505</v>
+        <v>1.034</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.0297</v>
+        <v>-1.0589</v>
       </c>
       <c r="V2" t="n">
-        <v>6.8005</v>
+        <v>4.1772</v>
       </c>
       <c r="W2" t="n">
-        <v>6.9378</v>
+        <v>4.328</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1373</v>
+        <v>-0.1509</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>16.0092</v>
+        <v>8.757300000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>14.4686</v>
+        <v>10.8659</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5404</v>
+        <v>-2.1087</v>
       </c>
       <c r="G3" t="n">
-        <v>9.3231</v>
+        <v>3.8193</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1255</v>
+        <v>4.9677</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1976</v>
+        <v>-1.1482</v>
       </c>
       <c r="J3" t="n">
-        <v>9.772600000000001</v>
+        <v>7.8666</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2394</v>
+        <v>5.7348</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5334</v>
+        <v>2.1318</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4495</v>
+        <v>-4.0473</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8861</v>
+        <v>-0.7671</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.336</v>
+        <v>-3.2801</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5288</v>
+        <v>3.672</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1475</v>
       </c>
       <c r="R3" t="n">
-        <v>6.5288</v>
+        <v>4.819500000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1845</v>
+        <v>0.7248999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9154</v>
+        <v>1.2909</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2691</v>
+        <v>-0.5659000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3418</v>
+        <v>0.5411</v>
       </c>
       <c r="W3" t="n">
-        <v>5.6112</v>
+        <v>2.8559</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.2694</v>
+        <v>-2.3149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>14.2681</v>
+        <v>7.8108</v>
       </c>
       <c r="E4" t="n">
-        <v>15.2434</v>
+        <v>7.3942</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9749000000000003</v>
+        <v>0.4166</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5392</v>
+        <v>4.611400000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>8.5389</v>
+        <v>2.112</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.9997</v>
+        <v>2.4995</v>
       </c>
       <c r="J4" t="n">
-        <v>10.5755</v>
+        <v>5.1003</v>
       </c>
       <c r="K4" t="n">
-        <v>8.805199999999999</v>
+        <v>1.7591</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7703</v>
+        <v>3.3412</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.0365</v>
+        <v>-0.4889</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2663</v>
+        <v>0.3529</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.77</v>
+        <v>-0.8417000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>7.6944</v>
+        <v>3.2129</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1658</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>8.860300000000001</v>
+        <v>3.2129</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8972</v>
+        <v>-0.7055</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3569</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4597</v>
+        <v>-0.1435</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1372000000000001</v>
+        <v>0.6919</v>
       </c>
       <c r="W4" t="n">
-        <v>3.4765</v>
+        <v>2.8559</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.3392</v>
+        <v>-2.164</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>11.5642</v>
+        <v>7.5423</v>
       </c>
       <c r="E5" t="n">
-        <v>4.368600000000001</v>
+        <v>5.3467</v>
       </c>
       <c r="F5" t="n">
-        <v>7.1954</v>
+        <v>2.1958</v>
       </c>
       <c r="G5" t="n">
-        <v>7.0305</v>
+        <v>5.1716</v>
       </c>
       <c r="H5" t="n">
-        <v>8.5024</v>
+        <v>6.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4719</v>
+        <v>-0.8691000000000002</v>
       </c>
       <c r="J5" t="n">
-        <v>9.490500000000001</v>
+        <v>8.1988</v>
       </c>
       <c r="K5" t="n">
-        <v>7.587400000000001</v>
+        <v>6.502000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9033</v>
+        <v>1.6968</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.46</v>
+        <v>-3.0273</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9153</v>
+        <v>-0.4614</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.3752</v>
+        <v>-2.5659</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3317</v>
+        <v>0.6885</v>
       </c>
       <c r="Q5" t="n">
-        <v>-9.326700000000001</v>
+        <v>-5.7375</v>
       </c>
       <c r="R5" t="n">
-        <v>11.6584</v>
+        <v>6.4259</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4089</v>
+        <v>1.2922</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0026</v>
+        <v>0.7211</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4063</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7927999999999997</v>
+        <v>0.3901000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2019</v>
+        <v>2.164</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4091</v>
+        <v>-1.7739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>9.077500000000001</v>
+        <v>3.5205</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0146</v>
+        <v>0.4095999999999997</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0632</v>
+        <v>3.1108</v>
       </c>
       <c r="G6" t="n">
-        <v>9.970700000000001</v>
+        <v>0.4542000000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6033</v>
+        <v>1.1106</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3671</v>
+        <v>-0.6563000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>6.806699999999999</v>
+        <v>0.4439000000000006</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5283</v>
+        <v>-0.1859000000000002</v>
       </c>
       <c r="L6" t="n">
-        <v>3.278</v>
+        <v>0.6299</v>
       </c>
       <c r="M6" t="n">
-        <v>3.164000000000001</v>
+        <v>0.01040000000000019</v>
       </c>
       <c r="N6" t="n">
-        <v>3.075</v>
+        <v>1.2966</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08899999999999952</v>
+        <v>-1.2861</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6321</v>
+        <v>2.0655</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.8291</v>
+        <v>-2.295</v>
       </c>
       <c r="R6" t="n">
-        <v>7.4612</v>
+        <v>4.3605</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7416</v>
+        <v>2.7122</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5581</v>
+        <v>2.5883</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1835</v>
+        <v>0.1239000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-6.266500000000001</v>
+        <v>-1.7114</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4791</v>
+        <v>-0.3277</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.7458</v>
+        <v>-1.3838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.585500000000001</v>
+        <v>1.7714</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.490600000000001</v>
+        <v>-0.5114000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>8.0761</v>
+        <v>2.2828</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2059999999999997</v>
+        <v>2.3655</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7071999999999994</v>
+        <v>1.8467</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5011000000000001</v>
+        <v>0.5187999999999997</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.6936</v>
+        <v>2.1847</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.6106</v>
+        <v>0.3796000000000004</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9171</v>
+        <v>1.8051</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4875</v>
+        <v>0.1808999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9035</v>
+        <v>1.4671</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4160999999999999</v>
+        <v>-1.2862</v>
       </c>
       <c r="P7" t="n">
-        <v>4.197000000000001</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4974</v>
+        <v>-4.5899</v>
       </c>
       <c r="R7" t="n">
-        <v>7.6946</v>
+        <v>4.3605</v>
       </c>
       <c r="S7" t="n">
-        <v>4.369</v>
+        <v>2.7305</v>
       </c>
       <c r="T7" t="n">
-        <v>4.4623</v>
+        <v>1.051</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09309999999999999</v>
+        <v>1.6794</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7747</v>
+        <v>-3.0952</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7618</v>
+        <v>0.8428</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.0129</v>
+        <v>-3.938</v>
       </c>
     </row>
     <row r="8">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5034000000000001</v>
+        <v>0.1451000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9981</v>
+        <v>0.6149</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5017</v>
+        <v>-0.4697999999999998</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.8939</v>
+        <v>-5.3773</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6922</v>
+        <v>-1.517</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.201700000000001</v>
+        <v>-3.8604</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.025400000000001</v>
+        <v>-2.0799</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.928</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.0976</v>
+        <v>-1.3213</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8687</v>
+        <v>-3.2974</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2357999999999998</v>
+        <v>-0.7583</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.104299999999999</v>
+        <v>-2.5391</v>
       </c>
       <c r="P8" t="n">
-        <v>7.2282</v>
+        <v>2.9834</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R8" t="n">
-        <v>9.559799999999999</v>
+        <v>5.2784</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3092</v>
+        <v>1.6077</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4034</v>
+        <v>1.832</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0942</v>
+        <v>-0.2242999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>1.86</v>
+        <v>0.9312</v>
       </c>
       <c r="W8" t="n">
-        <v>4.9556</v>
+        <v>3.1577</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.0956</v>
+        <v>-2.2265</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1438</v>
+        <v>0.0815</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6204</v>
+        <v>2.7115</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4766</v>
+        <v>-2.63</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8222</v>
+        <v>-0.7977</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4278</v>
+        <v>0.3646</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.25</v>
+        <v>-1.1622</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1227</v>
+        <v>2.3281</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4181</v>
+        <v>1.4493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7046</v>
+        <v>0.8788</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9449</v>
+        <v>-3.1258</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9903</v>
+        <v>-1.0847</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9546</v>
+        <v>-2.041</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8675</v>
+        <v>0.8137</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4977</v>
+        <v>0.3834</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3698</v>
+        <v>0.4303</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="10">
@@ -1186,43 +1186,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.252</v>
+        <v>-1.66</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5504</v>
+        <v>-1.2197</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7018</v>
+        <v>-0.4403</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8542</v>
+        <v>-1.4374</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.353</v>
+        <v>-0.6291</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5012</v>
+        <v>-0.8083</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.2358</v>
+        <v>-1.4987</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.699</v>
+        <v>-0.7644</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5368</v>
+        <v>-0.7343</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3816</v>
+        <v>0.0613</v>
       </c>
       <c r="N10" t="n">
-        <v>0.346</v>
+        <v>0.1352</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0356</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,22 +1234,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1232</v>
+        <v>-0.0717</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6854</v>
+        <v>0.279</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8088</v>
+        <v>-0.3508</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2746</v>
+        <v>-0.1509</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2746</v>
+        <v>-0.1509</v>
       </c>
     </row>
     <row r="11">
@@ -1264,67 +1264,67 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8007</v>
+        <v>-2.0332</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.4449</v>
+        <v>-6.1104</v>
       </c>
       <c r="F11" t="n">
-        <v>9.6442</v>
+        <v>4.0773</v>
       </c>
       <c r="G11" t="n">
-        <v>4.484</v>
+        <v>1.14</v>
       </c>
       <c r="H11" t="n">
-        <v>6.5721</v>
+        <v>3.2585</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0881</v>
+        <v>-2.1186</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0073</v>
+        <v>1.4622</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1622</v>
+        <v>1.4593</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1549</v>
+        <v>0.002899999999999903</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4767</v>
+        <v>-0.3222</v>
       </c>
       <c r="N11" t="n">
-        <v>3.41</v>
+        <v>1.7993</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9335</v>
+        <v>-2.1214</v>
       </c>
       <c r="P11" t="n">
-        <v>-10.0262</v>
+        <v>-4.360399999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-16.3218</v>
+        <v>-8.032399999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>6.2956</v>
+        <v>3.672</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5306</v>
+        <v>-0.04570000000000002</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4024</v>
+        <v>-0.7733</v>
       </c>
       <c r="U11" t="n">
-        <v>0.872</v>
+        <v>0.7276</v>
       </c>
       <c r="V11" t="n">
-        <v>2.2719</v>
+        <v>1.2329</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2719</v>
+        <v>1.2329</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.9418</v>
+        <v>-4.8387</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5171</v>
+        <v>-2.6745</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4247</v>
+        <v>-2.1642</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.1733</v>
+        <v>-3.7073</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7682</v>
+        <v>-1.7269</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4051</v>
+        <v>-1.9804</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5487000000000002</v>
+        <v>-0.04559999999999997</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.9793</v>
+        <v>-1.918</v>
       </c>
       <c r="L12" t="n">
-        <v>2.4306</v>
+        <v>1.8725</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.6246</v>
+        <v>-3.6617</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2111</v>
+        <v>0.1911</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.836</v>
+        <v>-3.853</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.399</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.829</v>
+        <v>-3.4425</v>
       </c>
       <c r="R12" t="n">
-        <v>4.43</v>
+        <v>2.754</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0949</v>
+        <v>-0.292</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2065</v>
+        <v>-0.2686</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8883</v>
+        <v>-0.02349999999999985</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2746</v>
+        <v>-0.1509</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.3419</v>
+        <v>-1.2329</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.2616</v>
+        <v>-7.6827</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.9781</v>
+        <v>-7.5549</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7165</v>
+        <v>-0.1277999999999997</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.711500000000001</v>
+        <v>-6.6372</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.8003</v>
+        <v>-2.5042</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.9108</v>
+        <v>-4.1331</v>
       </c>
       <c r="J13" t="n">
-        <v>-11.3522</v>
+        <v>-6.8448</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.7069</v>
+        <v>-3.9711</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.6453</v>
+        <v>-2.8737</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6411</v>
+        <v>0.2076</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9065</v>
+        <v>1.4671</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2654999999999998</v>
+        <v>-1.2593</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2332000000000001</v>
+        <v>0.4589999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.6634</v>
+        <v>-2.295</v>
       </c>
       <c r="R13" t="n">
-        <v>4.43</v>
+        <v>2.754</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0449</v>
+        <v>-0.4226</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8331</v>
+        <v>0.3521</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8782</v>
+        <v>-0.7745000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.2719</v>
+        <v>-1.082</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2046</v>
+        <v>1.2329</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.4765</v>
+        <v>-2.3149</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>50.28489999999999</v>
+        <v>26.57680000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>10.8621</v>
+        <v>18.6904</v>
       </c>
       <c r="F14" t="n">
-        <v>39.42310000000001</v>
+        <v>7.886700000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>26.88410000000001</v>
+        <v>11.8282</v>
       </c>
       <c r="H14" t="n">
-        <v>37.56</v>
+        <v>23.6505</v>
       </c>
       <c r="I14" t="n">
-        <v>-10.6757</v>
+        <v>-11.822</v>
       </c>
       <c r="J14" t="n">
-        <v>32.8789</v>
+        <v>30.3517</v>
       </c>
       <c r="K14" t="n">
-        <v>22.6757</v>
+        <v>20.1509</v>
       </c>
       <c r="L14" t="n">
-        <v>10.2031</v>
+        <v>10.201</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.994899999999999</v>
+        <v>-18.5235</v>
       </c>
       <c r="N14" t="n">
-        <v>14.8847</v>
+        <v>3.4999</v>
       </c>
       <c r="O14" t="n">
-        <v>-20.8801</v>
+        <v>-22.0228</v>
       </c>
       <c r="P14" t="n">
-        <v>13.9898</v>
+        <v>5.737400000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-65.28660000000001</v>
+        <v>-39.01460000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>79.27660000000003</v>
+        <v>44.75209999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>9.136200000000001</v>
+        <v>8.319000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>13.8257</v>
+        <v>7.927899999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.689500000000001</v>
+        <v>0.3909000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2745999999999991</v>
+        <v>0.6920000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>29.4441</v>
+        <v>19.4244</v>
       </c>
       <c r="X14" t="n">
-        <v>-29.1696</v>
+        <v>-18.7327</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1625</v>
+        <v>21.2077</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4185</v>
+        <v>16.0969</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7442</v>
+        <v>5.1105</v>
       </c>
       <c r="G2" t="n">
-        <v>12.2231</v>
+        <v>17.7638</v>
       </c>
       <c r="H2" t="n">
-        <v>10.3269</v>
+        <v>14.7656</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8963</v>
+        <v>2.998</v>
       </c>
       <c r="J2" t="n">
-        <v>13.2361</v>
+        <v>19.6908</v>
       </c>
       <c r="K2" t="n">
-        <v>10.4648</v>
+        <v>16.0401</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7713</v>
+        <v>3.6507</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0131</v>
+        <v>-1.9271</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1379</v>
+        <v>-1.2745</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8751000000000002</v>
+        <v>-0.6528000000000003</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.213</v>
+        <v>-3.7435</v>
       </c>
       <c r="Q2" t="n">
-        <v>-9.1798</v>
+        <v>-12.8685</v>
       </c>
       <c r="R2" t="n">
-        <v>5.9669</v>
+        <v>9.1249</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0247</v>
+        <v>0.007300000000000029</v>
       </c>
       <c r="T2" t="n">
-        <v>1.034</v>
+        <v>1.8258</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0589</v>
+        <v>-1.8186</v>
       </c>
       <c r="V2" t="n">
-        <v>4.1772</v>
+        <v>7.1803</v>
       </c>
       <c r="W2" t="n">
-        <v>4.328</v>
+        <v>7.4489</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1509</v>
+        <v>-0.2686</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.757300000000001</v>
+        <v>16.8889</v>
       </c>
       <c r="E3" t="n">
-        <v>10.8659</v>
+        <v>18.3851</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1087</v>
+        <v>-1.4961</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8193</v>
+        <v>9.1624</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9677</v>
+        <v>8.254200000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1482</v>
+        <v>0.9082</v>
       </c>
       <c r="J3" t="n">
-        <v>7.8666</v>
+        <v>14.0901</v>
       </c>
       <c r="K3" t="n">
-        <v>5.7348</v>
+        <v>9.492800000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1318</v>
+        <v>4.597300000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.0473</v>
+        <v>-4.9277</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7671</v>
+        <v>-1.2387</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.2801</v>
+        <v>-3.6891</v>
       </c>
       <c r="P3" t="n">
-        <v>3.672</v>
+        <v>4.2114</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1475</v>
+        <v>-3.5097</v>
       </c>
       <c r="R3" t="n">
-        <v>4.819500000000001</v>
+        <v>7.7211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7248999999999999</v>
+        <v>1.521</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2909</v>
+        <v>2.3496</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5659000000000001</v>
+        <v>-0.8285</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5411</v>
+        <v>1.9939</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8559</v>
+        <v>5.4549</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3149</v>
+        <v>-3.4609</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>7.8108</v>
+        <v>11.578</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3942</v>
+        <v>9.747499999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4166</v>
+        <v>1.8303</v>
       </c>
       <c r="G4" t="n">
-        <v>4.611400000000001</v>
+        <v>10.3563</v>
       </c>
       <c r="H4" t="n">
-        <v>2.112</v>
+        <v>9.7453</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4995</v>
+        <v>0.6110000000000002</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1003</v>
+        <v>14.3162</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7591</v>
+        <v>10.3287</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3412</v>
+        <v>3.9874</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4889</v>
+        <v>-3.9598</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3529</v>
+        <v>-0.5834999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8417000000000001</v>
+        <v>-3.3764</v>
       </c>
       <c r="P4" t="n">
-        <v>3.2129</v>
+        <v>0.4679</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-9.3589</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2129</v>
+        <v>9.826799999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7055</v>
+        <v>2.3498</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5620000000000001</v>
+        <v>1.4636</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1435</v>
+        <v>0.8862</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6919</v>
+        <v>-1.5962</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8559</v>
+        <v>3.3266</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.164</v>
+        <v>-4.922800000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>7.5423</v>
+        <v>9.5898</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3467</v>
+        <v>5.7859</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1958</v>
+        <v>3.8039</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1716</v>
+        <v>5.1256</v>
       </c>
       <c r="H5" t="n">
-        <v>6.0407</v>
+        <v>6.815399999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8691000000000002</v>
+        <v>-1.6896</v>
       </c>
       <c r="J5" t="n">
-        <v>8.1988</v>
+        <v>6.0438</v>
       </c>
       <c r="K5" t="n">
-        <v>6.502000000000001</v>
+        <v>4.8724</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6968</v>
+        <v>1.1712</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0273</v>
+        <v>-0.9180000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4614</v>
+        <v>1.9428</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.5659</v>
+        <v>-2.861</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6885</v>
+        <v>3.7435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.7375</v>
+        <v>-3.5097</v>
       </c>
       <c r="R5" t="n">
-        <v>6.4259</v>
+        <v>7.2532</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2922</v>
+        <v>4.1712</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7211</v>
+        <v>4.7034</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5711000000000001</v>
+        <v>-0.5321</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3901000000000001</v>
+        <v>-3.4508</v>
       </c>
       <c r="W5" t="n">
-        <v>2.164</v>
+        <v>-1.4516</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7739</v>
+        <v>-1.9992</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5205</v>
+        <v>7.6778</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4095999999999997</v>
+        <v>7.0937</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1108</v>
+        <v>0.5841</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4542000000000002</v>
+        <v>4.7425</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1106</v>
+        <v>2.2462</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6563000000000001</v>
+        <v>2.4963</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4439000000000006</v>
+        <v>4.9638</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1859000000000002</v>
+        <v>1.672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6299</v>
+        <v>3.2918</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01040000000000019</v>
+        <v>-0.2212999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2966</v>
+        <v>0.5742</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2861</v>
+        <v>-0.7955000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0655</v>
+        <v>3.2756</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.295</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.3605</v>
+        <v>3.2756</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7122</v>
+        <v>-1.0068</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5883</v>
+        <v>-0.6647000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1239000000000001</v>
+        <v>-0.3421</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7114</v>
+        <v>0.6664</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3277</v>
+        <v>2.7946</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3838</v>
+        <v>-2.1283</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7714</v>
+        <v>5.1351</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5114000000000001</v>
+        <v>4.7817</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2828</v>
+        <v>0.3533999999999997</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3655</v>
+        <v>-2.0187</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8467</v>
+        <v>1.9812</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5187999999999997</v>
+        <v>-3.9998</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1847</v>
+        <v>1.8109</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3796000000000004</v>
+        <v>3.7042</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8051</v>
+        <v>-1.8934</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1808999999999998</v>
+        <v>-3.8296</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4671</v>
+        <v>-1.7232</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2862</v>
+        <v>-2.1064</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2295</v>
+        <v>3.9774</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5899</v>
+        <v>-4.6794</v>
       </c>
       <c r="R7" t="n">
-        <v>4.3605</v>
+        <v>8.657</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7305</v>
+        <v>2.2466</v>
       </c>
       <c r="T7" t="n">
-        <v>1.051</v>
+        <v>2.3245</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6794</v>
+        <v>-0.07790000000000002</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.0952</v>
+        <v>0.9298</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8428</v>
+        <v>5.325699999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.938</v>
+        <v>-4.3959</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1451000000000001</v>
+        <v>0.3468</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6149</v>
+        <v>4.596200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4697999999999998</v>
+        <v>-4.2496</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.3773</v>
+        <v>-2.5342</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.517</v>
+        <v>1.1446</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.8604</v>
+        <v>-3.6788</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0799</v>
+        <v>3.6391</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7586000000000001</v>
+        <v>2.8947</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3213</v>
+        <v>0.7442999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.2974</v>
+        <v>-6.1731</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7583</v>
+        <v>-1.7501</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.5391</v>
+        <v>-4.423</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9834</v>
+        <v>3.7436</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.295</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5.2784</v>
+        <v>3.7436</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6077</v>
+        <v>2.3297</v>
       </c>
       <c r="T8" t="n">
-        <v>1.832</v>
+        <v>0.9573</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2242999999999999</v>
+        <v>1.3724</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9312</v>
+        <v>-3.1923</v>
       </c>
       <c r="W8" t="n">
-        <v>3.1577</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2265</v>
+        <v>-3.1923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>A. CARDENAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0815</v>
+        <v>-0.8077000000000005</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7115</v>
+        <v>1.9976</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.63</v>
+        <v>-2.8052</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7977</v>
+        <v>-1.955499999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3646</v>
+        <v>-0.03049999999999997</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1622</v>
+        <v>-1.9249</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3281</v>
+        <v>4.1653</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4493</v>
+        <v>-1.7131</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8788</v>
+        <v>5.8784</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1258</v>
+        <v>-6.1207</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0847</v>
+        <v>1.6826</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.041</v>
+        <v>-7.8033</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1475</v>
+        <v>0.7019</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.6796</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1475</v>
+        <v>5.381399999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8137</v>
+        <v>0.7142000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>0.3834</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4303</v>
+        <v>0.3308</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.082</v>
+        <v>-0.2686</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.1282</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.082</v>
+        <v>-2.3968</v>
       </c>
     </row>
     <row r="10">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.66</v>
+        <v>-1.0756</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2197</v>
+        <v>-0.2374999999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4403</v>
+        <v>-0.8381000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4374</v>
+        <v>-1.3299</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6291</v>
+        <v>-0.8136</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8083</v>
+        <v>-0.5164</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4987</v>
+        <v>-1.3933</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7644</v>
+        <v>-0.7686000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7343</v>
+        <v>-0.6247</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0613</v>
+        <v>0.0635</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1352</v>
+        <v>-0.0449</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.1083</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.4679</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.4679</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0717</v>
+        <v>-0.0793</v>
       </c>
       <c r="T10" t="n">
-        <v>0.279</v>
+        <v>0.0917</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3508</v>
+        <v>-0.1711</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0641</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1509</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="11">
@@ -1264,67 +1264,67 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0332</v>
+        <v>-4.865399999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.1104</v>
+        <v>-9.021799999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0773</v>
+        <v>4.1563</v>
       </c>
       <c r="G11" t="n">
-        <v>1.14</v>
+        <v>-3.201</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2585</v>
+        <v>2.9292</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1186</v>
+        <v>-6.1303</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4622</v>
+        <v>-0.5124</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4593</v>
+        <v>-0.009800000000000031</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002899999999999903</v>
+        <v>-0.5026000000000003</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3222</v>
+        <v>-2.6886</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7993</v>
+        <v>2.9391</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.1214</v>
+        <v>-5.6276</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.360399999999999</v>
+        <v>-3.7434</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.032399999999999</v>
+        <v>-9.3589</v>
       </c>
       <c r="R11" t="n">
-        <v>3.672</v>
+        <v>5.615399999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.04570000000000002</v>
+        <v>0.7466</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7733</v>
+        <v>-0.4831000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7276</v>
+        <v>1.2295</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2329</v>
+        <v>1.3327</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2329</v>
+        <v>1.3327</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CARDENAS</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8387</v>
+        <v>-9.5733</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6745</v>
+        <v>-13.7946</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1642</v>
+        <v>4.2214</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7073</v>
+        <v>-4.121</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7269</v>
+        <v>-2.0937</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9804</v>
+        <v>-2.0273</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.04559999999999997</v>
+        <v>-2.1228</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.918</v>
+        <v>-4.3775</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8725</v>
+        <v>2.2549</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.6617</v>
+        <v>-1.9981</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1911</v>
+        <v>2.2839</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.853</v>
+        <v>-4.2822</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6885</v>
+        <v>-6.5511</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4425</v>
+        <v>-14.0384</v>
       </c>
       <c r="R12" t="n">
-        <v>2.754</v>
+        <v>7.4871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.292</v>
+        <v>4.9525</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2686</v>
+        <v>2.2272</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.02349999999999985</v>
+        <v>2.7254</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1509</v>
+        <v>-3.8536</v>
       </c>
       <c r="W12" t="n">
-        <v>1.082</v>
+        <v>0.1395</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2329</v>
+        <v>-3.993</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.6827</v>
+        <v>-12.4572</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.5549</v>
+        <v>-11.6495</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1277999999999997</v>
+        <v>-0.8074999999999997</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.6372</v>
+        <v>-11.2722</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5042</v>
+        <v>-1.5077</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.1331</v>
+        <v>-9.764600000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.8448</v>
+        <v>-8.535600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.9711</v>
+        <v>-3.1186</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.8737</v>
+        <v>-5.4171</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2076</v>
+        <v>-2.7366</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4671</v>
+        <v>1.6109</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2593</v>
+        <v>-4.3475</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4589999999999999</v>
+        <v>0.468</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.295</v>
+        <v>-5.849299999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>2.754</v>
+        <v>6.317299999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4226</v>
+        <v>-0.4594</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3521</v>
+        <v>0.6021000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7745000000000001</v>
+        <v>-1.0616</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.082</v>
+        <v>-1.1932</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2329</v>
+        <v>2.1334</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3149</v>
+        <v>-3.3266</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>26.57680000000001</v>
+        <v>43.64490000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>18.6904</v>
+        <v>33.7812</v>
       </c>
       <c r="F14" t="n">
-        <v>7.886700000000002</v>
+        <v>9.8634</v>
       </c>
       <c r="G14" t="n">
-        <v>11.8282</v>
+        <v>20.7181</v>
       </c>
       <c r="H14" t="n">
-        <v>23.6505</v>
+        <v>43.4362</v>
       </c>
       <c r="I14" t="n">
-        <v>-11.822</v>
+        <v>-22.7182</v>
       </c>
       <c r="J14" t="n">
-        <v>30.3517</v>
+        <v>56.1559</v>
       </c>
       <c r="K14" t="n">
-        <v>20.1509</v>
+        <v>39.0173</v>
       </c>
       <c r="L14" t="n">
-        <v>10.201</v>
+        <v>17.1382</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.5235</v>
+        <v>-35.43710000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4999</v>
+        <v>4.4186</v>
       </c>
       <c r="O14" t="n">
-        <v>-22.0228</v>
+        <v>-39.8565</v>
       </c>
       <c r="P14" t="n">
-        <v>5.737400000000001</v>
+        <v>7.0192</v>
       </c>
       <c r="Q14" t="n">
-        <v>-39.01460000000001</v>
+        <v>-67.8524</v>
       </c>
       <c r="R14" t="n">
-        <v>44.75209999999999</v>
+        <v>74.87130000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>8.319000000000001</v>
+        <v>17.4934</v>
       </c>
       <c r="T14" t="n">
-        <v>7.927899999999999</v>
+        <v>15.7808</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3909000000000001</v>
+        <v>1.7124</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6920000000000002</v>
+        <v>-1.585900000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>19.4244</v>
+        <v>29.697</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.7327</v>
+        <v>-31.2828</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -565,73 +565,73 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>21.2077</v>
+        <v>23.0825</v>
       </c>
       <c r="E2" t="n">
-        <v>16.0969</v>
+        <v>14.4017</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1105</v>
+        <v>8.6807</v>
       </c>
       <c r="G2" t="n">
-        <v>17.7638</v>
+        <v>16.6836</v>
       </c>
       <c r="H2" t="n">
-        <v>14.7656</v>
+        <v>5.657300000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>2.998</v>
+        <v>11.0263</v>
       </c>
       <c r="J2" t="n">
-        <v>19.6908</v>
+        <v>17.2918</v>
       </c>
       <c r="K2" t="n">
-        <v>16.0401</v>
+        <v>7.923800000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6507</v>
+        <v>9.367700000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9271</v>
+        <v>-0.6082</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2745</v>
+        <v>-2.2665</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6528000000000003</v>
+        <v>1.6584</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.7435</v>
+        <v>-2.3207</v>
       </c>
       <c r="Q2" t="n">
-        <v>-12.8685</v>
+        <v>-12.9961</v>
       </c>
       <c r="R2" t="n">
-        <v>9.1249</v>
+        <v>10.6753</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007300000000000029</v>
+        <v>1.7533</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8258</v>
+        <v>2.4627</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.8186</v>
+        <v>-0.7093999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>7.1803</v>
+        <v>6.9661</v>
       </c>
       <c r="W2" t="n">
-        <v>7.4489</v>
+        <v>7.6434</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2686</v>
+        <v>-0.6772</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16.8889</v>
+        <v>12.1556</v>
       </c>
       <c r="E3" t="n">
-        <v>18.3851</v>
+        <v>5.5769</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4961</v>
+        <v>6.5785</v>
       </c>
       <c r="G3" t="n">
-        <v>9.1624</v>
+        <v>5.9757</v>
       </c>
       <c r="H3" t="n">
-        <v>8.254200000000001</v>
+        <v>5.5454</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9082</v>
+        <v>0.4303</v>
       </c>
       <c r="J3" t="n">
-        <v>14.0901</v>
+        <v>5.4208</v>
       </c>
       <c r="K3" t="n">
-        <v>9.492800000000001</v>
+        <v>4.2435</v>
       </c>
       <c r="L3" t="n">
-        <v>4.597300000000001</v>
+        <v>1.1774</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.9277</v>
+        <v>0.5548000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2387</v>
+        <v>1.3019</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.6891</v>
+        <v>-0.7471</v>
       </c>
       <c r="P3" t="n">
-        <v>4.2114</v>
+        <v>5.1055</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.5097</v>
+        <v>-2.5529</v>
       </c>
       <c r="R3" t="n">
-        <v>7.7211</v>
+        <v>7.6584</v>
       </c>
       <c r="S3" t="n">
-        <v>1.521</v>
+        <v>3.8359</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3496</v>
+        <v>4.1161</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8285</v>
+        <v>-0.2803</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9939</v>
+        <v>-2.7617</v>
       </c>
       <c r="W3" t="n">
-        <v>5.4549</v>
+        <v>-1.4072</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.4609</v>
+        <v>-1.3544</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>11.578</v>
+        <v>12.1104</v>
       </c>
       <c r="E4" t="n">
-        <v>9.747499999999999</v>
+        <v>6.264900000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8303</v>
+        <v>5.8454</v>
       </c>
       <c r="G4" t="n">
-        <v>10.3563</v>
+        <v>8.4587</v>
       </c>
       <c r="H4" t="n">
-        <v>9.7453</v>
+        <v>5.1014</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6110000000000002</v>
+        <v>3.3573</v>
       </c>
       <c r="J4" t="n">
-        <v>14.3162</v>
+        <v>9.486599999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>10.3287</v>
+        <v>5.6606</v>
       </c>
       <c r="L4" t="n">
-        <v>3.9874</v>
+        <v>3.826</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.9598</v>
+        <v>-1.0279</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5834999999999999</v>
+        <v>-0.5593</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.3764</v>
+        <v>-0.4687000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4679</v>
+        <v>3.9452</v>
       </c>
       <c r="Q4" t="n">
-        <v>-9.3589</v>
+        <v>-7.1943</v>
       </c>
       <c r="R4" t="n">
-        <v>9.826799999999999</v>
+        <v>11.1395</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3498</v>
+        <v>1.8782</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4636</v>
+        <v>1.1519</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8862</v>
+        <v>0.7263000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5962</v>
+        <v>-2.1717</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3266</v>
+        <v>2.8206</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.922800000000001</v>
+        <v>-4.9923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>9.5898</v>
+        <v>8.2196</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7859</v>
+        <v>7.379100000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8039</v>
+        <v>0.8407000000000002</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1256</v>
+        <v>1.1161</v>
       </c>
       <c r="H5" t="n">
-        <v>6.815399999999999</v>
+        <v>3.9791</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6896</v>
+        <v>-2.863</v>
       </c>
       <c r="J5" t="n">
-        <v>6.0438</v>
+        <v>4.763500000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8724</v>
+        <v>5.2008</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1712</v>
+        <v>-0.4371999999999998</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9180000000000001</v>
+        <v>-3.6473</v>
       </c>
       <c r="N5" t="n">
-        <v>1.9428</v>
+        <v>-1.2217</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.861</v>
+        <v>-2.4257</v>
       </c>
       <c r="P5" t="n">
-        <v>3.7435</v>
+        <v>4.1772</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.5097</v>
+        <v>-3.4812</v>
       </c>
       <c r="R5" t="n">
-        <v>7.2532</v>
+        <v>7.6584</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1712</v>
+        <v>0.9242</v>
       </c>
       <c r="T5" t="n">
-        <v>4.7034</v>
+        <v>1.6684</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5321</v>
+        <v>-0.7443</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.4508</v>
+        <v>2.0022</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.4516</v>
+        <v>4.4282</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9992</v>
+        <v>-2.426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>7.6778</v>
+        <v>7.9894</v>
       </c>
       <c r="E6" t="n">
-        <v>7.0937</v>
+        <v>5.1357</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5841</v>
+        <v>2.8537</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7425</v>
+        <v>-1.6315</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2462</v>
+        <v>1.671</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4963</v>
+        <v>-3.3025</v>
       </c>
       <c r="J6" t="n">
-        <v>4.9638</v>
+        <v>1.0207</v>
       </c>
       <c r="K6" t="n">
-        <v>1.672</v>
+        <v>4.2267</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2918</v>
+        <v>-3.206300000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2212999999999999</v>
+        <v>-2.651899999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5742</v>
+        <v>-2.5558</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7955000000000001</v>
+        <v>-0.09630000000000005</v>
       </c>
       <c r="P6" t="n">
-        <v>3.2756</v>
+        <v>6.2659</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.4811</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2756</v>
+        <v>9.747</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0068</v>
+        <v>1.8887</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6647000000000001</v>
+        <v>2.3494</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3421</v>
+        <v>-0.4608</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6664</v>
+        <v>1.4663</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7946</v>
+        <v>5.246600000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1283</v>
+        <v>-3.7805</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.1351</v>
+        <v>7.8503</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7817</v>
+        <v>7.2426</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3533999999999997</v>
+        <v>0.6077</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0187</v>
+        <v>4.6349</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9812</v>
+        <v>2.1122</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.9998</v>
+        <v>2.5227</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8109</v>
+        <v>4.996700000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7042</v>
+        <v>1.6922</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8934</v>
+        <v>3.3045</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.8296</v>
+        <v>-0.3618</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7232</v>
+        <v>0.42</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1064</v>
+        <v>-0.7817000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9774</v>
+        <v>3.249</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.6794</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>8.657</v>
+        <v>3.249</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2466</v>
+        <v>-0.7108</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3245</v>
+        <v>-0.5747</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07790000000000002</v>
+        <v>-0.1361</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9298</v>
+        <v>0.6772</v>
       </c>
       <c r="W7" t="n">
-        <v>5.325699999999999</v>
+        <v>2.8206</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.3959</v>
+        <v>-2.1435</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3468</v>
+        <v>4.5546</v>
       </c>
       <c r="E8" t="n">
-        <v>4.596200000000001</v>
+        <v>-2.3691</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2496</v>
+        <v>6.9237</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5342</v>
+        <v>2.5544</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1446</v>
+        <v>-2.3046</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.6788</v>
+        <v>4.859100000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6391</v>
+        <v>2.9267</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8947</v>
+        <v>-2.1092</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7442999999999999</v>
+        <v>5.0359</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.1731</v>
+        <v>-0.3721999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7501</v>
+        <v>-0.1955</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.423</v>
+        <v>-0.1767000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7436</v>
+        <v>-1.3924</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-10.6754</v>
       </c>
       <c r="R8" t="n">
-        <v>3.7436</v>
+        <v>9.282900000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3297</v>
+        <v>5.2817</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9573</v>
+        <v>3.2066</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3724</v>
+        <v>2.0749</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1923</v>
+        <v>-1.889</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.1729</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.1923</v>
+        <v>-4.061900000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CARDENAS</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8077000000000005</v>
+        <v>1.2937</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9976</v>
+        <v>1.3413</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8052</v>
+        <v>-0.04760000000000009</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.955499999999999</v>
+        <v>-4.807</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.03049999999999997</v>
+        <v>-1.1988</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9249</v>
+        <v>-3.6081</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1653</v>
+        <v>-1.3881</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7131</v>
+        <v>1.558</v>
       </c>
       <c r="L9" t="n">
-        <v>5.8784</v>
+        <v>-2.9461</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.1207</v>
+        <v>-3.4187</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6826</v>
+        <v>-2.7568</v>
       </c>
       <c r="O9" t="n">
-        <v>-7.8033</v>
+        <v>-0.6621999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7019</v>
+        <v>3.713200000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.6796</v>
+        <v>-1.1604</v>
       </c>
       <c r="R9" t="n">
-        <v>5.381399999999999</v>
+        <v>4.8735</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7142000000000001</v>
+        <v>2.9515</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3834</v>
+        <v>1.7463</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3308</v>
+        <v>1.2051</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2686</v>
+        <v>-0.5641000000000003</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3968</v>
+        <v>-2.7075</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>A. CARDENAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0756</v>
+        <v>0.2560999999999992</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2374999999999998</v>
+        <v>0.8135999999999997</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8381000000000001</v>
+        <v>-0.5574999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3299</v>
+        <v>-0.2801000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8136</v>
+        <v>-0.9124999999999996</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5164</v>
+        <v>0.6325000000000003</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3933</v>
+        <v>4.1065</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7686000000000001</v>
+        <v>-1.1134</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6247</v>
+        <v>5.2198</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0635</v>
+        <v>-4.3865</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0449</v>
+        <v>0.2007999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1083</v>
+        <v>-4.587499999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4679</v>
+        <v>1.1603</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.6416</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4679</v>
+        <v>5.8018</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0793</v>
+        <v>-0.03060000000000002</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0917</v>
+        <v>0.2770000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1711</v>
+        <v>-0.3074999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1343</v>
+        <v>-0.5935</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1984</v>
+        <v>-1.6652</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.865399999999999</v>
+        <v>-1.3413</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.021799999999999</v>
+        <v>-0.1774000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>4.1563</v>
+        <v>-1.1639</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.201</v>
+        <v>-1.6513</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9292</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.1303</v>
+        <v>-0.7174</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5124</v>
+        <v>-1.1839</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.009800000000000031</v>
+        <v>-0.5515</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5026000000000003</v>
+        <v>-0.6324000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6886</v>
+        <v>-0.4674</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9391</v>
+        <v>-0.3825</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.6276</v>
+        <v>-0.08499999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.7434</v>
+        <v>0.6962</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9.3589</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>5.615399999999999</v>
+        <v>0.6962</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7466</v>
+        <v>-0.245</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4831000000000001</v>
+        <v>-0.06520000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2295</v>
+        <v>-0.1798</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3327</v>
+        <v>-0.1413</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3327</v>
+        <v>1.0717</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.213</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.5733</v>
+        <v>-6.3347</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.7946</v>
+        <v>-12.2283</v>
       </c>
       <c r="F12" t="n">
-        <v>4.2214</v>
+        <v>5.8935</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.121</v>
+        <v>-5.6583</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0937</v>
+        <v>1.0749</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0273</v>
+        <v>-6.7333</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1228</v>
+        <v>-4.8358</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.3775</v>
+        <v>-0.4042999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>2.2549</v>
+        <v>-4.4317</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9981</v>
+        <v>-0.8223999999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2839</v>
+        <v>1.4792</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.2822</v>
+        <v>-2.3016</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.5511</v>
+        <v>-3.713</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.0384</v>
+        <v>-9.515000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>7.4871</v>
+        <v>5.8018</v>
       </c>
       <c r="S12" t="n">
-        <v>4.9525</v>
+        <v>1.6823</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2272</v>
+        <v>0.7681000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>2.7254</v>
+        <v>0.9141999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.8536</v>
+        <v>1.3543</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1395</v>
+        <v>1.3543</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.4572</v>
+        <v>-14.0152</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.6495</v>
+        <v>-14.8275</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8074999999999997</v>
+        <v>0.8122</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.2722</v>
+        <v>-9.5708</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5077</v>
+        <v>-3.1616</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.764600000000002</v>
+        <v>-6.409000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.535600000000001</v>
+        <v>-7.498699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.1186</v>
+        <v>-2.6117</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.4171</v>
+        <v>-4.886900000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.7366</v>
+        <v>-2.0721</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6109</v>
+        <v>-0.5501</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.3475</v>
+        <v>-1.522</v>
       </c>
       <c r="P13" t="n">
-        <v>0.468</v>
+        <v>-2.3207</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.849299999999999</v>
+        <v>-9.2829</v>
       </c>
       <c r="R13" t="n">
-        <v>6.317299999999999</v>
+        <v>6.9622</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4594</v>
+        <v>0.3011</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6021000000000001</v>
+        <v>0.9941</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0616</v>
+        <v>-0.6931</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1932</v>
+        <v>-2.4249</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1334</v>
+        <v>0.9598000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.3266</v>
+        <v>-3.3847</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>43.64490000000001</v>
+        <v>55.82100000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>33.7812</v>
+        <v>18.55350000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>9.8634</v>
+        <v>37.26709999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>20.7181</v>
+        <v>15.8244</v>
       </c>
       <c r="H14" t="n">
-        <v>43.4362</v>
+        <v>16.6298</v>
       </c>
       <c r="I14" t="n">
-        <v>-22.7182</v>
+        <v>-0.8050999999999995</v>
       </c>
       <c r="J14" t="n">
-        <v>56.1559</v>
+        <v>35.10679999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>39.0173</v>
+        <v>23.7155</v>
       </c>
       <c r="L14" t="n">
-        <v>17.1382</v>
+        <v>11.3907</v>
       </c>
       <c r="M14" t="n">
-        <v>-35.43710000000001</v>
+        <v>-19.2816</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4186</v>
+        <v>-7.0863</v>
       </c>
       <c r="O14" t="n">
-        <v>-39.8565</v>
+        <v>-12.1961</v>
       </c>
       <c r="P14" t="n">
-        <v>7.0192</v>
+        <v>18.5657</v>
       </c>
       <c r="Q14" t="n">
-        <v>-67.8524</v>
+        <v>-64.98090000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>74.87130000000001</v>
+        <v>83.54599999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>17.4934</v>
+        <v>19.5105</v>
       </c>
       <c r="T14" t="n">
-        <v>15.7808</v>
+        <v>18.1007</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7124</v>
+        <v>1.4092</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.585900000000002</v>
+        <v>1.9199</v>
       </c>
       <c r="W14" t="n">
-        <v>29.697</v>
+        <v>30.326</v>
       </c>
       <c r="X14" t="n">
-        <v>-31.2828</v>
+        <v>-28.4062</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>23.0825</v>
+        <v>26.31</v>
       </c>
       <c r="E2" t="n">
-        <v>14.4017</v>
+        <v>18.7926</v>
       </c>
       <c r="F2" t="n">
-        <v>8.6807</v>
+        <v>7.517300000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>16.6836</v>
+        <v>14.4898</v>
       </c>
       <c r="H2" t="n">
-        <v>5.657300000000001</v>
+        <v>6.233200000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>11.0263</v>
+        <v>8.256399999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>17.2918</v>
+        <v>17.4091</v>
       </c>
       <c r="K2" t="n">
-        <v>7.923800000000001</v>
+        <v>8.1531</v>
       </c>
       <c r="L2" t="n">
-        <v>9.367700000000001</v>
+        <v>9.256</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6082</v>
+        <v>-2.9194</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2665</v>
+        <v>-1.9198</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6584</v>
+        <v>-0.9999</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.3207</v>
+        <v>-0.4676</v>
       </c>
       <c r="Q2" t="n">
-        <v>-12.9961</v>
+        <v>-13.0909</v>
       </c>
       <c r="R2" t="n">
-        <v>10.6753</v>
+        <v>12.6233</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7533</v>
+        <v>2.5683</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4627</v>
+        <v>3.0224</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7093999999999999</v>
+        <v>-0.4541000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>6.9661</v>
+        <v>9.7195</v>
       </c>
       <c r="W2" t="n">
-        <v>7.6434</v>
+        <v>11.452</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6772</v>
+        <v>-1.7325</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>12.1556</v>
+        <v>15.3843</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5769</v>
+        <v>7.960100000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>6.5785</v>
+        <v>7.4242</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9757</v>
+        <v>7.310499999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5454</v>
+        <v>6.7569</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4303</v>
+        <v>0.5536999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4208</v>
+        <v>7.3306</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2435</v>
+        <v>5.4995</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1774</v>
+        <v>1.831</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5548000000000002</v>
+        <v>-0.01999999999999991</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3019</v>
+        <v>1.2575</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7471</v>
+        <v>-1.2775</v>
       </c>
       <c r="P3" t="n">
-        <v>5.1055</v>
+        <v>6.3117</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5529</v>
+        <v>-2.5714</v>
       </c>
       <c r="R3" t="n">
-        <v>7.6584</v>
+        <v>8.8832</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8359</v>
+        <v>3.6141</v>
       </c>
       <c r="T3" t="n">
-        <v>4.1161</v>
+        <v>4.5125</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2803</v>
+        <v>-0.8984999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.7617</v>
+        <v>-1.8519</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.4072</v>
+        <v>-1.3116</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3544</v>
+        <v>-0.5403</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>12.1104</v>
+        <v>10.5868</v>
       </c>
       <c r="E4" t="n">
-        <v>6.264900000000001</v>
+        <v>10.0527</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8454</v>
+        <v>0.5339999999999998</v>
       </c>
       <c r="G4" t="n">
-        <v>8.4587</v>
+        <v>0.7183999999999995</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1014</v>
+        <v>6.069400000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3573</v>
+        <v>-5.3511</v>
       </c>
       <c r="J4" t="n">
-        <v>9.486599999999999</v>
+        <v>6.1343</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6606</v>
+        <v>8.3057</v>
       </c>
       <c r="L4" t="n">
-        <v>3.826</v>
+        <v>-2.1713</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0279</v>
+        <v>-5.4159</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5593</v>
+        <v>-2.2362</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4687000000000001</v>
+        <v>-3.1797</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9452</v>
+        <v>7.7143</v>
       </c>
       <c r="Q4" t="n">
-        <v>-7.1943</v>
+        <v>-3.5065</v>
       </c>
       <c r="R4" t="n">
-        <v>11.1395</v>
+        <v>11.2208</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8782</v>
+        <v>1.7569</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1519</v>
+        <v>2.2277</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7263000000000001</v>
+        <v>-0.4708000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1717</v>
+        <v>0.3974</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8206</v>
+        <v>5.1973</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.9923</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>8.2196</v>
+        <v>8.4757</v>
       </c>
       <c r="E5" t="n">
-        <v>7.379100000000001</v>
+        <v>8.0261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8407000000000002</v>
+        <v>0.4496999999999998</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1161</v>
+        <v>-1.9581</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9791</v>
+        <v>3.2416</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.863</v>
+        <v>-5.1998</v>
       </c>
       <c r="J5" t="n">
-        <v>4.763500000000001</v>
+        <v>4.3675</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2008</v>
+        <v>5.6358</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4371999999999998</v>
+        <v>-1.2682</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.6473</v>
+        <v>-6.325600000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2217</v>
+        <v>-2.3943</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4257</v>
+        <v>-3.9314</v>
       </c>
       <c r="P5" t="n">
-        <v>4.1772</v>
+        <v>4.4415</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4812</v>
+        <v>-4.6752</v>
       </c>
       <c r="R5" t="n">
-        <v>7.6584</v>
+        <v>9.116900000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9242</v>
+        <v>2.9325</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6684</v>
+        <v>2.874</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7443</v>
+        <v>0.0585</v>
       </c>
       <c r="V5" t="n">
-        <v>2.0022</v>
+        <v>3.0598</v>
       </c>
       <c r="W5" t="n">
-        <v>4.4282</v>
+        <v>5.4597</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.426</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7.9894</v>
+        <v>7.8834</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1357</v>
+        <v>7.1502</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8537</v>
+        <v>0.7332</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6315</v>
+        <v>4.6638</v>
       </c>
       <c r="H6" t="n">
-        <v>1.671</v>
+        <v>2.1171</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.3025</v>
+        <v>2.5466</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0207</v>
+        <v>4.9198</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2267</v>
+        <v>1.6425</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.206300000000001</v>
+        <v>3.2773</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.651899999999999</v>
+        <v>-0.2561</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.5558</v>
+        <v>0.4746</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.09630000000000005</v>
+        <v>-0.7306999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>6.2659</v>
+        <v>3.2727</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4811</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>9.747</v>
+        <v>3.2727</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8887</v>
+        <v>-0.7206999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3494</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4608</v>
+        <v>-0.1536</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4663</v>
+        <v>0.6675</v>
       </c>
       <c r="W6" t="n">
-        <v>5.246600000000001</v>
+        <v>2.7974</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.7805</v>
+        <v>-2.1299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>7.8503</v>
+        <v>6.4981</v>
       </c>
       <c r="E7" t="n">
-        <v>7.2426</v>
+        <v>2.3357</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6077</v>
+        <v>4.1624</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6349</v>
+        <v>0.9713000000000003</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1122</v>
+        <v>5.6978</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5227</v>
+        <v>-4.7265</v>
       </c>
       <c r="J7" t="n">
-        <v>4.996700000000001</v>
+        <v>5.5193</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6922</v>
+        <v>6.9392</v>
       </c>
       <c r="L7" t="n">
-        <v>3.3045</v>
+        <v>-1.4202</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3618</v>
+        <v>-4.547899999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.42</v>
+        <v>-1.2414</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7817000000000001</v>
+        <v>-3.3064</v>
       </c>
       <c r="P7" t="n">
-        <v>3.249</v>
+        <v>4.6753</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-8.4156</v>
       </c>
       <c r="R7" t="n">
-        <v>3.249</v>
+        <v>13.0908</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7108</v>
+        <v>2.4759</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5747</v>
+        <v>1.2347</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1361</v>
+        <v>1.2412</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6772</v>
+        <v>-1.6244</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8206</v>
+        <v>3.9974</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1435</v>
+        <v>-5.6218</v>
       </c>
     </row>
     <row r="8">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>4.5546</v>
+        <v>6.1121</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3691</v>
+        <v>0.7711000000000006</v>
       </c>
       <c r="F8" t="n">
-        <v>6.9237</v>
+        <v>5.341</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5544</v>
+        <v>3.6398</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3046</v>
+        <v>1.275</v>
       </c>
       <c r="I8" t="n">
-        <v>4.859100000000001</v>
+        <v>2.3647</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9267</v>
+        <v>5.444800000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.1092</v>
+        <v>1.181</v>
       </c>
       <c r="L8" t="n">
-        <v>5.0359</v>
+        <v>4.2634</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3721999999999998</v>
+        <v>-1.8051</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1955</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1767000000000001</v>
+        <v>-1.8988</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3924</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="Q8" t="n">
-        <v>-10.6754</v>
+        <v>-10.7532</v>
       </c>
       <c r="R8" t="n">
-        <v>9.282900000000001</v>
+        <v>10.7532</v>
       </c>
       <c r="S8" t="n">
-        <v>5.2817</v>
+        <v>5.5592</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2066</v>
+        <v>3.4095</v>
       </c>
       <c r="U8" t="n">
-        <v>2.0749</v>
+        <v>2.1497</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.889</v>
+        <v>-3.0867</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1729</v>
+        <v>2.6702</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.061900000000001</v>
+        <v>-5.7569</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>A. CARDENAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2937</v>
+        <v>-0.2767999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3413</v>
+        <v>1.1111</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.04760000000000009</v>
+        <v>-1.3879</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.807</v>
+        <v>-1.4937</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1988</v>
+        <v>-2.0618</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.6081</v>
+        <v>0.5680999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3881</v>
+        <v>4.3731</v>
       </c>
       <c r="K9" t="n">
-        <v>1.558</v>
+        <v>-1.6852</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.9461</v>
+        <v>6.058</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4187</v>
+        <v>-5.8668</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.7568</v>
+        <v>-0.3766999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6621999999999999</v>
+        <v>-5.4901</v>
       </c>
       <c r="P9" t="n">
-        <v>3.713200000000001</v>
+        <v>1.8701</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1604</v>
+        <v>-4.6752</v>
       </c>
       <c r="R9" t="n">
-        <v>4.8735</v>
+        <v>6.545400000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9515</v>
+        <v>0.1843</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7463</v>
+        <v>0.3484</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2051</v>
+        <v>-0.1642</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5641000000000003</v>
+        <v>-0.8373999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1434</v>
+        <v>1.0649</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7075</v>
+        <v>-1.9023</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CARDENAS</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2560999999999992</v>
+        <v>-1.2515</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8135999999999997</v>
+        <v>0.1827</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5574999999999999</v>
+        <v>-1.4342</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2801000000000001</v>
+        <v>-2.0484</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9124999999999996</v>
+        <v>-0.4561000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6325000000000003</v>
+        <v>-1.5923</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1065</v>
+        <v>-1.2096</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1134</v>
+        <v>-0.6049</v>
       </c>
       <c r="L10" t="n">
-        <v>5.2198</v>
+        <v>-0.6047</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.3865</v>
+        <v>-0.8388</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2007999999999999</v>
+        <v>0.1487999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.587499999999999</v>
+        <v>-0.9875</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1603</v>
+        <v>0.7013</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.6416</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5.8018</v>
+        <v>0.7013</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.03060000000000002</v>
+        <v>0.2306</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2770000000000001</v>
+        <v>0.3274</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3074999999999999</v>
+        <v>-0.09659999999999996</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5935</v>
+        <v>-0.1351</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0717</v>
+        <v>1.0649</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6652</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3413</v>
+        <v>-1.5325</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1774000000000002</v>
+        <v>0.1774</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1639</v>
+        <v>-1.7098</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6513</v>
+        <v>-7.9785</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-1.036</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7174</v>
+        <v>-6.942600000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1839</v>
+        <v>-1.298</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5515</v>
+        <v>2.4805</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6324000000000001</v>
+        <v>-3.7784</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4674</v>
+        <v>-6.6806</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3825</v>
+        <v>-3.5164</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.08499999999999999</v>
+        <v>-3.1642</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6962</v>
+        <v>4.909000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1688</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6962</v>
+        <v>6.0779</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.245</v>
+        <v>3.5589</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.06520000000000001</v>
+        <v>1.3092</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1798</v>
+        <v>2.2497</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1413</v>
+        <v>-2.0217</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0717</v>
+        <v>1.3351</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.213</v>
+        <v>-3.3568</v>
       </c>
     </row>
     <row r="12">
@@ -1342,67 +1342,67 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.3347</v>
+        <v>-7.5791</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.2283</v>
+        <v>-13.5616</v>
       </c>
       <c r="F12" t="n">
-        <v>5.8935</v>
+        <v>5.9825</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.6583</v>
+        <v>-6.682499999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0749</v>
+        <v>0.8264999999999998</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.7333</v>
+        <v>-7.5088</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.8358</v>
+        <v>-4.970499999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4042999999999999</v>
+        <v>-0.4417999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.4317</v>
+        <v>-4.5287</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8223999999999998</v>
+        <v>-1.712</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4792</v>
+        <v>1.2682</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.3016</v>
+        <v>-2.9801</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.713</v>
+        <v>-4.207799999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.515000000000001</v>
+        <v>-10.7532</v>
       </c>
       <c r="R12" t="n">
-        <v>5.8018</v>
+        <v>6.545500000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6823</v>
+        <v>1.976</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7681000000000001</v>
+        <v>0.8269999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9141999999999999</v>
+        <v>1.1491</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3543</v>
+        <v>1.3351</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3543</v>
+        <v>1.3351</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.0152</v>
+        <v>-11.8217</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.8275</v>
+        <v>-13.0077</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8122</v>
+        <v>1.1858</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.5708</v>
+        <v>-8.7799</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.1616</v>
+        <v>-2.9172</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.409000000000001</v>
+        <v>-5.8628</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.498699999999999</v>
+        <v>-5.352600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.6117</v>
+        <v>-1.5189</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.886900000000001</v>
+        <v>-3.833600000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0721</v>
+        <v>-3.4272</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5501</v>
+        <v>-1.3983</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.522</v>
+        <v>-2.029</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3207</v>
+        <v>-3.5065</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.2829</v>
+        <v>-11.6884</v>
       </c>
       <c r="R13" t="n">
-        <v>6.9622</v>
+        <v>8.181700000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3011</v>
+        <v>0.7541</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9941</v>
+        <v>0.9657999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6931</v>
+        <v>-0.2118</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.4249</v>
+        <v>-0.2892999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9598000000000001</v>
+        <v>3.0676</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.3847</v>
+        <v>-3.3569</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>55.82100000000001</v>
+        <v>58.78880000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>18.55350000000001</v>
+        <v>29.9904</v>
       </c>
       <c r="F14" t="n">
-        <v>37.26709999999999</v>
+        <v>28.7982</v>
       </c>
       <c r="G14" t="n">
-        <v>15.8244</v>
+        <v>2.852499999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>16.6298</v>
+        <v>25.7464</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8050999999999995</v>
+        <v>-22.8944</v>
       </c>
       <c r="J14" t="n">
-        <v>35.10679999999999</v>
+        <v>42.6678</v>
       </c>
       <c r="K14" t="n">
-        <v>23.7155</v>
+        <v>35.58649999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>11.3907</v>
+        <v>7.0806</v>
       </c>
       <c r="M14" t="n">
-        <v>-19.2816</v>
+        <v>-39.8154</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.0863</v>
+        <v>-9.840300000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.1961</v>
+        <v>-29.9753</v>
       </c>
       <c r="P14" t="n">
-        <v>18.5657</v>
+        <v>25.714</v>
       </c>
       <c r="Q14" t="n">
-        <v>-64.98090000000001</v>
+        <v>-71.2984</v>
       </c>
       <c r="R14" t="n">
-        <v>83.54599999999999</v>
+        <v>97.01270000000002</v>
       </c>
       <c r="S14" t="n">
-        <v>19.5105</v>
+        <v>24.8901</v>
       </c>
       <c r="T14" t="n">
-        <v>18.1007</v>
+        <v>20.4916</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4092</v>
+        <v>4.3986</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9199</v>
+        <v>5.3328</v>
       </c>
       <c r="W14" t="n">
-        <v>30.326</v>
+        <v>38.13</v>
       </c>
       <c r="X14" t="n">
-        <v>-28.4062</v>
+        <v>-32.7974</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>26.31</v>
+        <v>32.9573</v>
       </c>
       <c r="E2" t="n">
-        <v>18.7926</v>
+        <v>23.3938</v>
       </c>
       <c r="F2" t="n">
-        <v>7.517300000000001</v>
+        <v>9.563500000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>14.4898</v>
+        <v>19.632</v>
       </c>
       <c r="H2" t="n">
-        <v>6.233200000000001</v>
+        <v>10.7689</v>
       </c>
       <c r="I2" t="n">
-        <v>8.256399999999999</v>
+        <v>8.8629</v>
       </c>
       <c r="J2" t="n">
-        <v>17.4091</v>
+        <v>20.6581</v>
       </c>
       <c r="K2" t="n">
-        <v>8.1531</v>
+        <v>12.0554</v>
       </c>
       <c r="L2" t="n">
-        <v>9.256</v>
+        <v>8.602599999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9194</v>
+        <v>-1.0262</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.9198</v>
+        <v>-1.2863</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9999</v>
+        <v>0.2603999999999997</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4676</v>
+        <v>-1.4036</v>
       </c>
       <c r="Q2" t="n">
-        <v>-13.0909</v>
+        <v>-15.4405</v>
       </c>
       <c r="R2" t="n">
-        <v>12.6233</v>
+        <v>14.0369</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5683</v>
+        <v>2.8884</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0224</v>
+        <v>3.0086</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4541000000000001</v>
+        <v>-0.1202</v>
       </c>
       <c r="V2" t="n">
-        <v>9.7195</v>
+        <v>11.8406</v>
       </c>
       <c r="W2" t="n">
-        <v>11.452</v>
+        <v>15.1676</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7325</v>
+        <v>-3.327</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>15.3843</v>
+        <v>19.0567</v>
       </c>
       <c r="E3" t="n">
-        <v>7.960100000000001</v>
+        <v>8.2967</v>
       </c>
       <c r="F3" t="n">
-        <v>7.4242</v>
+        <v>10.7599</v>
       </c>
       <c r="G3" t="n">
-        <v>7.310499999999999</v>
+        <v>10.5873</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7569</v>
+        <v>9.021999999999998</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5536999999999999</v>
+        <v>1.5654</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3306</v>
+        <v>8.863</v>
       </c>
       <c r="K3" t="n">
-        <v>5.4995</v>
+        <v>6.9595</v>
       </c>
       <c r="L3" t="n">
-        <v>1.831</v>
+        <v>1.9033</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01999999999999991</v>
+        <v>1.7244</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2575</v>
+        <v>2.0626</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2775</v>
+        <v>-0.3381</v>
       </c>
       <c r="P3" t="n">
-        <v>6.3117</v>
+        <v>6.5505</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5714</v>
+        <v>-3.743</v>
       </c>
       <c r="R3" t="n">
-        <v>8.8832</v>
+        <v>10.2936</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6141</v>
+        <v>4.1706</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5125</v>
+        <v>4.891299999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8984999999999999</v>
+        <v>-0.7208000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8519</v>
+        <v>-2.2518</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.3116</v>
+        <v>-1.7143</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5403</v>
+        <v>-0.5376</v>
       </c>
     </row>
     <row r="4">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>10.5868</v>
+        <v>15.5193</v>
       </c>
       <c r="E4" t="n">
-        <v>10.0527</v>
+        <v>11.8223</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5339999999999998</v>
+        <v>3.696800000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7183999999999995</v>
+        <v>2.9832</v>
       </c>
       <c r="H4" t="n">
-        <v>6.069400000000001</v>
+        <v>6.3996</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.3511</v>
+        <v>-3.4166</v>
       </c>
       <c r="J4" t="n">
-        <v>6.1343</v>
+        <v>6.5356</v>
       </c>
       <c r="K4" t="n">
-        <v>8.3057</v>
+        <v>7.67</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.1713</v>
+        <v>-1.1344</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.4159</v>
+        <v>-3.5523</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2362</v>
+        <v>-1.2702</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.1797</v>
+        <v>-2.2821</v>
       </c>
       <c r="P4" t="n">
-        <v>7.7143</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.5065</v>
+        <v>-3.5092</v>
       </c>
       <c r="R4" t="n">
-        <v>11.2208</v>
+        <v>12.3992</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7569</v>
+        <v>2.1842</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2277</v>
+        <v>2.5399</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4708000000000001</v>
+        <v>-0.3556000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3974</v>
+        <v>1.4619</v>
       </c>
       <c r="W4" t="n">
-        <v>5.1973</v>
+        <v>6.2563</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.8</v>
+        <v>-4.7944</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8.4757</v>
+        <v>11.2729</v>
       </c>
       <c r="E5" t="n">
-        <v>8.0261</v>
+        <v>2.982699999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4496999999999998</v>
+        <v>8.290100000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9581</v>
+        <v>4.2798</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2416</v>
+        <v>5.4679</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.1998</v>
+        <v>-1.188</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3675</v>
+        <v>6.439100000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6358</v>
+        <v>6.0739</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2682</v>
+        <v>0.3649000000000002</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.325600000000001</v>
+        <v>-2.1591</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3943</v>
+        <v>-0.6059999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.9314</v>
+        <v>-1.553</v>
       </c>
       <c r="P5" t="n">
-        <v>4.4415</v>
+        <v>6.0825</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.6752</v>
+        <v>-8.422000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>9.116900000000001</v>
+        <v>14.5049</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9325</v>
+        <v>2.5335</v>
       </c>
       <c r="T5" t="n">
-        <v>2.874</v>
+        <v>0.9725999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0585</v>
+        <v>1.5609</v>
       </c>
       <c r="V5" t="n">
-        <v>3.0598</v>
+        <v>-1.6232</v>
       </c>
       <c r="W5" t="n">
-        <v>5.4597</v>
+        <v>3.9935</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4</v>
+        <v>-5.6167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>7.8834</v>
+        <v>10.9999</v>
       </c>
       <c r="E6" t="n">
-        <v>7.1502</v>
+        <v>2.184400000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7332</v>
+        <v>8.8154</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6638</v>
+        <v>7.6334</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1171</v>
+        <v>2.752400000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5466</v>
+        <v>4.881</v>
       </c>
       <c r="J6" t="n">
-        <v>4.9198</v>
+        <v>7.3724</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6425</v>
+        <v>1.8581</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2773</v>
+        <v>5.5143</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2561</v>
+        <v>0.2610000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4746</v>
+        <v>0.8943999999999998</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7306999999999999</v>
+        <v>-0.6332999999999998</v>
       </c>
       <c r="P6" t="n">
-        <v>3.2727</v>
+        <v>-0.2339000000000002</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-11.9312</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2727</v>
+        <v>11.6974</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7206999999999999</v>
+        <v>6.6857</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5669999999999999</v>
+        <v>4.0775</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1536</v>
+        <v>2.6082</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6675</v>
+        <v>-3.0851</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7974</v>
+        <v>2.666</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1299</v>
+        <v>-5.7511</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>6.4981</v>
+        <v>8.355499999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3357</v>
+        <v>7.946700000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1624</v>
+        <v>0.4088000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9713000000000003</v>
+        <v>-1.193</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6978</v>
+        <v>1.7738</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.7265</v>
+        <v>-2.9669</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5193</v>
+        <v>5.7785</v>
       </c>
       <c r="K7" t="n">
-        <v>6.9392</v>
+        <v>4.8542</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4202</v>
+        <v>0.9240999999999993</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.547899999999999</v>
+        <v>-6.9716</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2414</v>
+        <v>-3.0805</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.3064</v>
+        <v>-3.8908</v>
       </c>
       <c r="P7" t="n">
-        <v>4.6753</v>
+        <v>1.8716</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.4156</v>
+        <v>-8.187999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>13.0908</v>
+        <v>10.0598</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4759</v>
+        <v>2.888</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2347</v>
+        <v>3.0361</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2412</v>
+        <v>-0.1481</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6244</v>
+        <v>4.7889</v>
       </c>
       <c r="W7" t="n">
-        <v>3.9974</v>
+        <v>7.3205</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.6218</v>
+        <v>-2.5316</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>6.1121</v>
+        <v>7.880699999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7711000000000006</v>
+        <v>7.1339</v>
       </c>
       <c r="F8" t="n">
-        <v>5.341</v>
+        <v>0.7468</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6398</v>
+        <v>4.6554</v>
       </c>
       <c r="H8" t="n">
-        <v>1.275</v>
+        <v>2.1136</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3647</v>
+        <v>2.5418</v>
       </c>
       <c r="J8" t="n">
-        <v>5.444800000000001</v>
+        <v>4.919</v>
       </c>
       <c r="K8" t="n">
-        <v>1.181</v>
+        <v>1.6421</v>
       </c>
       <c r="L8" t="n">
-        <v>4.2634</v>
+        <v>3.2769</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8051</v>
+        <v>-0.2635</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.4716</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8988</v>
+        <v>-0.7350999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>3.2752</v>
       </c>
       <c r="Q8" t="n">
-        <v>-10.7532</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>10.7532</v>
+        <v>3.2752</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5592</v>
+        <v>-0.7163</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4095</v>
+        <v>-0.5799</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1497</v>
+        <v>-0.1364</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.0867</v>
+        <v>0.6665</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6702</v>
+        <v>2.7949</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.7569</v>
+        <v>-2.1284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CARDENAS</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2767999999999999</v>
+        <v>-0.1721000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1111</v>
+        <v>2.0207</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3879</v>
+        <v>-2.1929</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4937</v>
+        <v>-0.8227</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0618</v>
+        <v>0.5509000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5680999999999999</v>
+        <v>-1.3738</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3731</v>
+        <v>0.274</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6852</v>
+        <v>0.4188999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>6.058</v>
+        <v>-0.1450000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.8668</v>
+        <v>-1.0968</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3766999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.4901</v>
+        <v>-1.2289</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8701</v>
+        <v>1.1697</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.6752</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>6.545400000000001</v>
+        <v>1.1697</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1843</v>
+        <v>0.4162</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3484</v>
+        <v>0.6825999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1642</v>
+        <v>-0.2663</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8373999999999999</v>
+        <v>-0.9352999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0649</v>
+        <v>1.0642</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9023</v>
+        <v>-1.9995</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>A. CARDENAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2515</v>
+        <v>-0.2034000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1827</v>
+        <v>1.7193</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4342</v>
+        <v>-1.9229</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0484</v>
+        <v>-0.2567999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4561000000000001</v>
+        <v>-1.8842</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5923</v>
+        <v>1.6273</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2096</v>
+        <v>5.713900000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6049</v>
+        <v>-1.1548</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6047</v>
+        <v>6.8687</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8388</v>
+        <v>-5.9706</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1487999999999999</v>
+        <v>-0.7292999999999998</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9875</v>
+        <v>-5.2414</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7013</v>
+        <v>1.1698</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-5.8485</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7013</v>
+        <v>7.0183</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2306</v>
+        <v>0.2489</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3274</v>
+        <v>0.79</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.09659999999999996</v>
+        <v>-0.5411000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1351</v>
+        <v>-1.3654</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0649</v>
+        <v>1.0642</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2</v>
+        <v>-2.4296</v>
       </c>
     </row>
     <row r="11">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5325</v>
+        <v>-0.2977000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1774</v>
+        <v>1.6332</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7098</v>
+        <v>-1.931</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.9785</v>
+        <v>-6.253</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.036</v>
+        <v>-0.3635999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.942600000000001</v>
+        <v>-5.8896</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.298</v>
+        <v>0.4864999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4805</v>
+        <v>3.8247</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.7784</v>
+        <v>-3.3382</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.6806</v>
+        <v>-6.7397</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.5164</v>
+        <v>-4.1884</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.1642</v>
+        <v>-2.5514</v>
       </c>
       <c r="P11" t="n">
-        <v>4.909000000000001</v>
+        <v>3.7431</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1688</v>
+        <v>-2.3394</v>
       </c>
       <c r="R11" t="n">
-        <v>6.0779</v>
+        <v>6.0826</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5589</v>
+        <v>3.8352</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3092</v>
+        <v>1.6211</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2497</v>
+        <v>2.2141</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0217</v>
+        <v>-1.6232</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3351</v>
+        <v>1.8651</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3568</v>
+        <v>-3.4883</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,67 +1342,67 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5791</v>
+        <v>-1.0356</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.5616</v>
+        <v>-1.0467</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9825</v>
+        <v>0.0111</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.682499999999999</v>
+        <v>-1.2681</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8264999999999998</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.5088</v>
+        <v>-0.2928</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.970499999999999</v>
+        <v>-0.7331</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4417999999999999</v>
+        <v>-0.8063</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.5287</v>
+        <v>0.0732</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.712</v>
+        <v>-0.5351</v>
       </c>
       <c r="N12" t="n">
-        <v>1.2682</v>
+        <v>-0.169</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.9801</v>
+        <v>-0.3661</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.207799999999999</v>
+        <v>-0.7018</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.7532</v>
+        <v>-1.1697</v>
       </c>
       <c r="R12" t="n">
-        <v>6.545500000000001</v>
+        <v>0.4679</v>
       </c>
       <c r="S12" t="n">
-        <v>1.976</v>
+        <v>-0.1299</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8269999999999998</v>
+        <v>-0.2081</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1491</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3351</v>
+        <v>1.0642</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3351</v>
+        <v>1.0642</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,148 +1420,226 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.8217</v>
+        <v>-5.2972</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.0077</v>
+        <v>-10.0554</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1858</v>
+        <v>4.7584</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.7799</v>
+        <v>-3.441099999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.9172</v>
+        <v>1.1874</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.8628</v>
+        <v>-4.628500000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.352600000000001</v>
+        <v>-0.7545000000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.5189</v>
+        <v>0.4428999999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.833600000000001</v>
+        <v>-1.1974</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.4272</v>
+        <v>-2.686599999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3983</v>
+        <v>0.7444999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.029</v>
+        <v>-3.4311</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.5065</v>
+        <v>-4.913</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.6884</v>
+        <v>-11.9312</v>
       </c>
       <c r="R13" t="n">
-        <v>8.181700000000001</v>
+        <v>7.0183</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7541</v>
+        <v>1.8583</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9657999999999999</v>
+        <v>1.2975</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2118</v>
+        <v>0.5607</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2892999999999999</v>
+        <v>1.1986</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0676</v>
+        <v>1.333</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.3569</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>S. DE LARREA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Valencia Basket</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-13.2181</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-11.7418</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.4763</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-8.543699999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-4.5224</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4.0212</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-4.844599999999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-2.2766</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-2.5678</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-3.699</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-2.2459</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.4533</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-3.2753</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-11.6974</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8.422000000000001</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.08950000000000014</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.6722</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.5827</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.4888</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4.1279</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-5.6167</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Valencia Basket</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>58.78880000000002</v>
-      </c>
-      <c r="E14" t="n">
-        <v>29.9904</v>
-      </c>
-      <c r="F14" t="n">
-        <v>28.7982</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.852499999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>25.7464</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-22.8944</v>
-      </c>
-      <c r="J14" t="n">
-        <v>42.6678</v>
-      </c>
-      <c r="K14" t="n">
-        <v>35.58649999999999</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7.0806</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-39.8154</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-9.840300000000001</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-29.9753</v>
-      </c>
-      <c r="P14" t="n">
-        <v>25.714</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-71.2984</v>
-      </c>
-      <c r="R14" t="n">
-        <v>97.01270000000002</v>
-      </c>
-      <c r="S14" t="n">
-        <v>24.8901</v>
-      </c>
-      <c r="T14" t="n">
-        <v>20.4916</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.3986</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.3328</v>
-      </c>
-      <c r="W14" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-32.7974</v>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>85.81819999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>46.28980000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>39.5277</v>
+      </c>
+      <c r="G15" t="n">
+        <v>27.9927</v>
+      </c>
+      <c r="H15" t="n">
+        <v>32.291</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-4.298999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>60.70790000000001</v>
+      </c>
+      <c r="K15" t="n">
+        <v>41.562</v>
+      </c>
+      <c r="L15" t="n">
+        <v>19.1452</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-32.7151</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-9.2705</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-23.4442</v>
+      </c>
+      <c r="P15" t="n">
+        <v>22.2248</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-84.2201</v>
+      </c>
+      <c r="R15" t="n">
+        <v>106.4458</v>
+      </c>
+      <c r="S15" t="n">
+        <v>26.9523</v>
+      </c>
+      <c r="T15" t="n">
+        <v>22.80139999999999</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.1509</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.6479</v>
+      </c>
+      <c r="W15" t="n">
+        <v>47.00309999999999</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-38.35530000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total_NP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Off_NP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Def_NP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Net_Shooting</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Net_2P</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net_3P</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Off_Shooting</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Off_2P</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Off_3P</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Def_Shooting</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Def_2P</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Def_3P</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Net_TOV</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Off_TOV</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Def_TOV</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Net_ORB</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Off_ORB</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Def_ORB</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Net_FT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Off_FT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Def_FT</t>
         </is>
@@ -562,76 +550,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>32.9573</v>
+        <v>53.4064</v>
       </c>
       <c r="E2" t="n">
-        <v>23.3938</v>
+        <v>39.3829</v>
       </c>
       <c r="F2" t="n">
-        <v>9.563500000000001</v>
+        <v>14.0235</v>
       </c>
       <c r="G2" t="n">
-        <v>19.632</v>
+        <v>32.4801</v>
       </c>
       <c r="H2" t="n">
-        <v>10.7689</v>
+        <v>14.171</v>
       </c>
       <c r="I2" t="n">
-        <v>8.8629</v>
+        <v>18.3091</v>
       </c>
       <c r="J2" t="n">
-        <v>20.6581</v>
+        <v>34.2348</v>
       </c>
       <c r="K2" t="n">
-        <v>12.0554</v>
+        <v>15.6602</v>
       </c>
       <c r="L2" t="n">
-        <v>8.602599999999999</v>
+        <v>18.5746</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0262</v>
+        <v>-1.7548</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2863</v>
+        <v>-1.489</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2603999999999997</v>
+        <v>-0.2656000000000002</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4036</v>
+        <v>-0.468</v>
       </c>
       <c r="Q2" t="n">
-        <v>-15.4405</v>
+        <v>-18.9508</v>
       </c>
       <c r="R2" t="n">
-        <v>14.0369</v>
+        <v>18.4832</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8884</v>
+        <v>4.2335</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0086</v>
+        <v>3.6117</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1202</v>
+        <v>0.6218000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>11.8406</v>
+        <v>17.1607</v>
       </c>
       <c r="W2" t="n">
-        <v>15.1676</v>
+        <v>20.4874</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.327</v>
+        <v>-3.3267</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +628,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>19.0567</v>
+        <v>22.3255</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2967</v>
+        <v>8.262599999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>10.7599</v>
+        <v>14.0632</v>
       </c>
       <c r="G3" t="n">
-        <v>10.5873</v>
+        <v>9.3888</v>
       </c>
       <c r="H3" t="n">
-        <v>9.021999999999998</v>
+        <v>4.9716</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5654</v>
+        <v>4.4172</v>
       </c>
       <c r="J3" t="n">
-        <v>8.863</v>
+        <v>8.914199999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>6.9595</v>
+        <v>3.6148</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9033</v>
+        <v>5.299399999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7244</v>
+        <v>0.4747999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>2.0626</v>
+        <v>1.3569</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3381</v>
+        <v>-0.8821000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5505</v>
+        <v>2.1056</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.743</v>
+        <v>-13.1019</v>
       </c>
       <c r="R3" t="n">
-        <v>10.2936</v>
+        <v>15.2076</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1706</v>
+        <v>7.4022</v>
       </c>
       <c r="T3" t="n">
-        <v>4.891299999999999</v>
+        <v>3.9318</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7208000000000001</v>
+        <v>3.4704</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.2518</v>
+        <v>3.429</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.7143</v>
+        <v>8.5184</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5376</v>
+        <v>-5.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +706,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>15.5193</v>
+        <v>19.7001</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8223</v>
+        <v>8.5284</v>
       </c>
       <c r="F4" t="n">
-        <v>3.696800000000001</v>
+        <v>11.1717</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9832</v>
+        <v>10.7144</v>
       </c>
       <c r="H4" t="n">
-        <v>6.3996</v>
+        <v>9.2486</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.4166</v>
+        <v>1.466</v>
       </c>
       <c r="J4" t="n">
-        <v>6.5356</v>
+        <v>10.0107</v>
       </c>
       <c r="K4" t="n">
-        <v>7.67</v>
+        <v>7.3753</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1344</v>
+        <v>2.6354</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.5523</v>
+        <v>0.704</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2702</v>
+        <v>1.8735</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2821</v>
+        <v>-1.1694</v>
       </c>
       <c r="P4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.422599999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.5092</v>
+        <v>-4.9132</v>
       </c>
       <c r="R4" t="n">
-        <v>12.3992</v>
+        <v>13.3358</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1842</v>
+        <v>5.2067</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5399</v>
+        <v>5.4094</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3556000000000001</v>
+        <v>-0.2025000000000002</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4619</v>
+        <v>-4.6437</v>
       </c>
       <c r="W4" t="n">
-        <v>6.2563</v>
+        <v>-1.9782</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.7944</v>
+        <v>-2.6655</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +784,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>11.2729</v>
+        <v>17.0149</v>
       </c>
       <c r="E5" t="n">
-        <v>2.982699999999999</v>
+        <v>6.0623</v>
       </c>
       <c r="F5" t="n">
-        <v>8.290100000000001</v>
+        <v>10.9526</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2798</v>
+        <v>4.1332</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4679</v>
+        <v>4.4069</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.188</v>
+        <v>-0.2737999999999992</v>
       </c>
       <c r="J5" t="n">
-        <v>6.439100000000001</v>
+        <v>8.9991</v>
       </c>
       <c r="K5" t="n">
-        <v>6.0739</v>
+        <v>6.371200000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3649000000000002</v>
+        <v>2.6282</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1591</v>
+        <v>-4.866099999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6059999999999999</v>
+        <v>-1.9639</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.553</v>
+        <v>-2.902200000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>6.0825</v>
+        <v>8.890699999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.422000000000001</v>
+        <v>-9.8264</v>
       </c>
       <c r="R5" t="n">
-        <v>14.5049</v>
+        <v>18.7171</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5335</v>
+        <v>3.6202</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9725999999999999</v>
+        <v>1.3002</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5609</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6232</v>
+        <v>0.3709</v>
       </c>
       <c r="W5" t="n">
-        <v>3.9935</v>
+        <v>5.5893</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.6167</v>
+        <v>-5.2185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +862,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>10.9999</v>
+        <v>15.3517</v>
       </c>
       <c r="E6" t="n">
-        <v>2.184400000000001</v>
+        <v>6.4076</v>
       </c>
       <c r="F6" t="n">
-        <v>8.8154</v>
+        <v>8.9442</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6334</v>
+        <v>1.4699</v>
       </c>
       <c r="H6" t="n">
-        <v>2.752400000000001</v>
+        <v>2.724200000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.881</v>
+        <v>-1.2541</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3724</v>
+        <v>4.177</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8581</v>
+        <v>5.0217</v>
       </c>
       <c r="L6" t="n">
-        <v>5.5143</v>
+        <v>-0.8446</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2610000000000003</v>
+        <v>-2.7071</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8943999999999998</v>
+        <v>-2.2976</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6332999999999998</v>
+        <v>-0.4094000000000002</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2339000000000002</v>
+        <v>9.358599999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-11.9312</v>
+        <v>-7.0188</v>
       </c>
       <c r="R6" t="n">
-        <v>11.6974</v>
+        <v>16.3775</v>
       </c>
       <c r="S6" t="n">
-        <v>6.6857</v>
+        <v>2.6635</v>
       </c>
       <c r="T6" t="n">
-        <v>4.0775</v>
+        <v>2.4614</v>
       </c>
       <c r="U6" t="n">
-        <v>2.6082</v>
+        <v>0.2020999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.0851</v>
+        <v>1.8597</v>
       </c>
       <c r="W6" t="n">
-        <v>2.666</v>
+        <v>6.7878</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.7511</v>
+        <v>-4.9282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +940,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>8.355499999999999</v>
+        <v>7.3927</v>
       </c>
       <c r="E7" t="n">
-        <v>7.946700000000001</v>
+        <v>6.4191</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4088000000000001</v>
+        <v>0.9737</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.193</v>
+        <v>3.3834</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7738</v>
+        <v>2.2518</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.9669</v>
+        <v>1.1316</v>
       </c>
       <c r="J7" t="n">
-        <v>5.7785</v>
+        <v>3.3107</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8542</v>
+        <v>1.4588</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9240999999999993</v>
+        <v>1.8519</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.9716</v>
+        <v>0.07269999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.0805</v>
+        <v>0.7931</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.8908</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8716</v>
+        <v>4.6793</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.187999999999999</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>10.0598</v>
+        <v>4.6793</v>
       </c>
       <c r="S7" t="n">
-        <v>2.888</v>
+        <v>0.1308</v>
       </c>
       <c r="T7" t="n">
-        <v>3.0361</v>
+        <v>0.3138</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1481</v>
+        <v>-0.183</v>
       </c>
       <c r="V7" t="n">
-        <v>4.7889</v>
+        <v>-0.8008</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3205</v>
+        <v>2.7947</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5316</v>
+        <v>-3.5955</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1018,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>7.880699999999999</v>
+        <v>5.4351</v>
       </c>
       <c r="E8" t="n">
-        <v>7.1339</v>
+        <v>5.1318</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7468</v>
+        <v>0.3033999999999998</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6554</v>
+        <v>-3.2887</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1136</v>
+        <v>-0.09919999999999959</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5418</v>
+        <v>-3.1895</v>
       </c>
       <c r="J8" t="n">
-        <v>4.919</v>
+        <v>7.096</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6421</v>
+        <v>5.6527</v>
       </c>
       <c r="L8" t="n">
-        <v>3.2769</v>
+        <v>1.4435</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2635</v>
+        <v>-10.3848</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4716</v>
+        <v>-5.752</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7350999999999999</v>
+        <v>-4.6328</v>
       </c>
       <c r="P8" t="n">
-        <v>3.2752</v>
+        <v>-1.1698</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-14.2716</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2752</v>
+        <v>13.1021</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7163</v>
+        <v>5.637</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5799</v>
+        <v>4.7189</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1364</v>
+        <v>0.9181999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6665</v>
+        <v>4.2566</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7949</v>
+        <v>7.5885</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1284</v>
+        <v>-3.332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1096,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1721000000000001</v>
+        <v>0.9953000000000003</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0207</v>
+        <v>-5.8863</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1929</v>
+        <v>6.8815</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8227</v>
+        <v>1.229699999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5509000000000001</v>
+        <v>2.124</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3738</v>
+        <v>-0.8942999999999994</v>
       </c>
       <c r="J9" t="n">
-        <v>0.274</v>
+        <v>4.702200000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4188999999999999</v>
+        <v>2.3952</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1450000000000001</v>
+        <v>2.306999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0968</v>
+        <v>-3.4724</v>
       </c>
       <c r="N9" t="n">
-        <v>0.132</v>
+        <v>-0.2710000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2289</v>
+        <v>-3.2011</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1697</v>
+        <v>-4.9132</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-14.2717</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1697</v>
+        <v>9.358499999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4162</v>
+        <v>2.8139</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6825999999999999</v>
+        <v>1.6842</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2663</v>
+        <v>1.1298</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9352999999999999</v>
+        <v>1.8648</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0642</v>
+        <v>1.9991</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9995</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CARDENAS</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1177,73 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2034000000000001</v>
+        <v>0.5595999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7193</v>
+        <v>3.9584</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9229</v>
+        <v>-3.3992</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2567999999999999</v>
+        <v>-6.6238</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8842</v>
+        <v>-1.6321</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6273</v>
+        <v>-4.9916</v>
       </c>
       <c r="J10" t="n">
-        <v>5.713900000000001</v>
+        <v>1.89</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1548</v>
+        <v>4.2315</v>
       </c>
       <c r="L10" t="n">
-        <v>6.8687</v>
+        <v>-2.341600000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.9706</v>
+        <v>-8.5137</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7292999999999998</v>
+        <v>-5.8638</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.2414</v>
+        <v>-2.649900000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1698</v>
+        <v>5.6151</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.8485</v>
+        <v>-2.5736</v>
       </c>
       <c r="R10" t="n">
-        <v>7.0183</v>
+        <v>8.188699999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2489</v>
+        <v>5.454</v>
       </c>
       <c r="T10" t="n">
-        <v>0.79</v>
+        <v>2.7773</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5411000000000001</v>
+        <v>2.6767</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3654</v>
+        <v>-3.8856</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0642</v>
+        <v>1.8649</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4296</v>
+        <v>-5.7504</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1255,67 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2977000000000001</v>
+        <v>-0.1716</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6332</v>
+        <v>2.02</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.931</v>
+        <v>-2.1917</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.253</v>
+        <v>-0.8230999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3635999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.8896</v>
+        <v>-1.3741</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4864999999999999</v>
+        <v>0.2763</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8247</v>
+        <v>0.4206</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.3382</v>
+        <v>-0.1441</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.7397</v>
+        <v>-1.0995</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.1884</v>
+        <v>0.1304999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.5514</v>
+        <v>-1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>3.7431</v>
+        <v>1.1698</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3394</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>6.0826</v>
+        <v>1.1698</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8352</v>
+        <v>0.4168</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6211</v>
+        <v>0.6795</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2141</v>
+        <v>-0.2625999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6232</v>
+        <v>-0.9349999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8651</v>
+        <v>1.0641</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.4883</v>
+        <v>-1.9991</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1333,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0356</v>
+        <v>-1.0353</v>
       </c>
       <c r="E12" t="n">
         <v>-1.0467</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0111</v>
+        <v>0.0114</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2681</v>
+        <v>-1.2678</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9752999999999999</v>
+        <v>-0.975</v>
       </c>
       <c r="I12" t="n">
         <v>-0.2928</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7331</v>
+        <v>-0.7326</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8063</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>0.0732</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5351</v>
+        <v>-0.5352</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.169</v>
+        <v>-0.1691</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3661</v>
+        <v>-0.366</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7018</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1697</v>
+        <v>-1.1698</v>
       </c>
       <c r="R12" t="n">
         <v>0.4679</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1299</v>
+        <v>-0.1298</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2081</v>
+        <v>-0.2084</v>
       </c>
       <c r="U12" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0642</v>
+        <v>1.0641</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0642</v>
+        <v>1.0641</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1399,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>A. CARDENAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1408,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2972</v>
+        <v>-2.8307</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.0554</v>
+        <v>0.3071000000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>4.7584</v>
+        <v>-3.1379</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.441099999999999</v>
+        <v>-3.278199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1874</v>
+        <v>-3.057799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.628500000000001</v>
+        <v>-0.2205000000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7545000000000002</v>
+        <v>4.627599999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4428999999999998</v>
+        <v>-0.8202</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1974</v>
+        <v>5.4482</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.686599999999999</v>
+        <v>-7.9059</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7444999999999999</v>
+        <v>-2.2372</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.4311</v>
+        <v>-5.6685</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.913</v>
+        <v>3.0415</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.9312</v>
+        <v>-6.083</v>
       </c>
       <c r="R13" t="n">
-        <v>7.0183</v>
+        <v>9.124499999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8583</v>
+        <v>0.3672000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2975</v>
+        <v>0.6984</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5607</v>
+        <v>-0.3311000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1986</v>
+        <v>-2.9611</v>
       </c>
       <c r="W13" t="n">
-        <v>1.333</v>
+        <v>1.0641</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1344</v>
+        <v>-4.0252</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1486,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.2181</v>
+        <v>-16.191</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.7418</v>
+        <v>-13.2798</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4763</v>
+        <v>-2.911</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.543699999999999</v>
+        <v>-10.8588</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.5224</v>
+        <v>-3.146</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.0212</v>
+        <v>-7.712999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.844599999999999</v>
+        <v>-3.9799</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.2766</v>
+        <v>-0.3809</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.5678</v>
+        <v>-3.599</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.699</v>
+        <v>-6.879</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2459</v>
+        <v>-2.7648</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4533</v>
+        <v>-4.114</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.2753</v>
+        <v>-4.4453</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.6974</v>
+        <v>-15.4414</v>
       </c>
       <c r="R14" t="n">
-        <v>8.422000000000001</v>
+        <v>10.9962</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08950000000000014</v>
+        <v>1.6662</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6722</v>
+        <v>1.8798</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5827</v>
+        <v>-0.2138000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4888</v>
+        <v>-2.5529</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1279</v>
+        <v>4.2618</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.6167</v>
+        <v>-6.8146</v>
       </c>
     </row>
     <row r="15">
@@ -1576,70 +1564,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>85.81819999999999</v>
+        <v>121.9526999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>46.28980000000001</v>
+        <v>66.26739999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>39.5277</v>
+        <v>55.6854</v>
       </c>
       <c r="G15" t="n">
-        <v>27.9927</v>
+        <v>36.6591</v>
       </c>
       <c r="H15" t="n">
-        <v>32.291</v>
+        <v>31.53900000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.298999999999999</v>
+        <v>5.120200000000004</v>
       </c>
       <c r="J15" t="n">
-        <v>60.70790000000001</v>
+        <v>83.52610000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>41.562</v>
+        <v>50.195</v>
       </c>
       <c r="L15" t="n">
-        <v>19.1452</v>
+        <v>33.3321</v>
       </c>
       <c r="M15" t="n">
-        <v>-32.7151</v>
+        <v>-46.867</v>
       </c>
       <c r="N15" t="n">
-        <v>-9.2705</v>
+        <v>-18.6544</v>
       </c>
       <c r="O15" t="n">
-        <v>-23.4442</v>
+        <v>-28.2113</v>
       </c>
       <c r="P15" t="n">
-        <v>22.2248</v>
+        <v>31.585</v>
       </c>
       <c r="Q15" t="n">
-        <v>-84.2201</v>
+        <v>-107.6222</v>
       </c>
       <c r="R15" t="n">
-        <v>106.4458</v>
+        <v>139.2081999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>26.9523</v>
+        <v>39.48219999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>22.80139999999999</v>
+        <v>29.258</v>
       </c>
       <c r="U15" t="n">
-        <v>4.1509</v>
+        <v>10.2247</v>
       </c>
       <c r="V15" t="n">
-        <v>8.6479</v>
+        <v>14.2267</v>
       </c>
       <c r="W15" t="n">
-        <v>47.00309999999999</v>
+        <v>61.106</v>
       </c>
       <c r="X15" t="n">
-        <v>-38.35530000000001</v>
+        <v>-46.8795</v>
       </c>
     </row>
   </sheetData>
